--- a/Vivienda/4_carga/ced_vivienda_gen.xlsx
+++ b/Vivienda/4_carga/ced_vivienda_gen.xlsx
@@ -786,7 +786,7 @@
         <v>7.9</v>
       </c>
       <c r="J14">
-        <v>0.52</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="15">
@@ -821,7 +821,7 @@
         <v>7.3</v>
       </c>
       <c r="J15">
-        <v>0.63</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="16">
@@ -856,7 +856,7 @@
         <v>7.6</v>
       </c>
       <c r="J16">
-        <v>0.55</v>
+        <v>44.26</v>
       </c>
     </row>
     <row r="17">
@@ -891,7 +891,7 @@
         <v>10.8</v>
       </c>
       <c r="J17">
-        <v>0.46</v>
+        <v>36.59</v>
       </c>
     </row>
     <row r="18">
@@ -926,7 +926,7 @@
         <v>10.4</v>
       </c>
       <c r="J18">
-        <v>0.55</v>
+        <v>43.84</v>
       </c>
     </row>
     <row r="19">
@@ -961,7 +961,7 @@
         <v>10.6</v>
       </c>
       <c r="J19">
-        <v>0.49</v>
+        <v>39.17</v>
       </c>
     </row>
     <row r="20">
@@ -996,7 +996,7 @@
         <v>12.7</v>
       </c>
       <c r="J20">
-        <v>0.43</v>
+        <v>34.12</v>
       </c>
     </row>
     <row r="21">
@@ -1031,7 +1031,7 @@
         <v>13.1</v>
       </c>
       <c r="J21">
-        <v>0.5600000000000001</v>
+        <v>44.43</v>
       </c>
     </row>
     <row r="22">
@@ -1066,7 +1066,7 @@
         <v>12.9</v>
       </c>
       <c r="J22">
-        <v>0.47</v>
+        <v>37.55</v>
       </c>
     </row>
     <row r="23">
@@ -1101,7 +1101,7 @@
         <v>13.85</v>
       </c>
       <c r="J23">
-        <v>0.41</v>
+        <v>32.73</v>
       </c>
     </row>
     <row r="24">
@@ -1136,7 +1136,7 @@
         <v>13.75</v>
       </c>
       <c r="J24">
-        <v>0.52</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="25">
@@ -1171,7 +1171,7 @@
         <v>13.8</v>
       </c>
       <c r="J25">
-        <v>0.44</v>
+        <v>35.56</v>
       </c>
     </row>
     <row r="26">
@@ -1206,7 +1206,7 @@
         <v>15.9</v>
       </c>
       <c r="J26">
-        <v>0.39</v>
+        <v>31.38</v>
       </c>
     </row>
     <row r="27">
@@ -1241,7 +1241,7 @@
         <v>15.1</v>
       </c>
       <c r="J27">
-        <v>0.5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28">
@@ -1276,7 +1276,7 @@
         <v>15.5</v>
       </c>
       <c r="J28">
-        <v>0.43</v>
+        <v>34.57</v>
       </c>
     </row>
     <row r="29">
@@ -1311,7 +1311,7 @@
         <v>13.5</v>
       </c>
       <c r="J29">
-        <v>0.37</v>
+        <v>29.46</v>
       </c>
     </row>
     <row r="30">
@@ -1346,7 +1346,7 @@
         <v>13.3</v>
       </c>
       <c r="J30">
-        <v>0.48</v>
+        <v>38.71</v>
       </c>
     </row>
     <row r="31">
@@ -1381,7 +1381,7 @@
         <v>13.4</v>
       </c>
       <c r="J31">
-        <v>0.41</v>
+        <v>32.83</v>
       </c>
     </row>
     <row r="32">
@@ -1419,7 +1419,7 @@
         <v>15.7</v>
       </c>
       <c r="J32">
-        <v>0.36</v>
+        <v>28.98</v>
       </c>
     </row>
     <row r="33">
@@ -1457,7 +1457,7 @@
         <v>15.9</v>
       </c>
       <c r="J33">
-        <v>0.48</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="34">
@@ -1495,7 +1495,7 @@
         <v>15.8</v>
       </c>
       <c r="J34">
-        <v>0.4</v>
+        <v>31.78</v>
       </c>
     </row>
     <row r="35">
@@ -1533,7 +1533,7 @@
         <v>13.9</v>
       </c>
       <c r="J35">
-        <v>0.37</v>
+        <v>29.31</v>
       </c>
     </row>
     <row r="36">
@@ -1571,7 +1571,7 @@
         <v>13.7</v>
       </c>
       <c r="J36">
-        <v>0.48</v>
+        <v>38.54</v>
       </c>
     </row>
     <row r="37">
@@ -1609,7 +1609,7 @@
         <v>13.8</v>
       </c>
       <c r="J37">
-        <v>0.41</v>
+        <v>32.56</v>
       </c>
     </row>
     <row r="38">
@@ -1647,7 +1647,7 @@
         <v>13.35</v>
       </c>
       <c r="J38">
-        <v>0.38</v>
+        <v>30.65</v>
       </c>
     </row>
     <row r="39">
@@ -1685,7 +1685,7 @@
         <v>13.05</v>
       </c>
       <c r="J39">
-        <v>0.51</v>
+        <v>40.66</v>
       </c>
     </row>
     <row r="40">
@@ -1723,7 +1723,7 @@
         <v>13.2</v>
       </c>
       <c r="J40">
-        <v>0.43</v>
+        <v>34.25</v>
       </c>
     </row>
     <row r="41">
@@ -1761,7 +1761,7 @@
         <v>11.3</v>
       </c>
       <c r="J41">
-        <v>0.4</v>
+        <v>32.22</v>
       </c>
     </row>
     <row r="42">
@@ -1799,7 +1799,7 @@
         <v>11.1</v>
       </c>
       <c r="J42">
-        <v>0.53</v>
+        <v>42.79</v>
       </c>
     </row>
     <row r="43">
@@ -1837,7 +1837,7 @@
         <v>11.2</v>
       </c>
       <c r="J43">
-        <v>0.45</v>
+        <v>36.03</v>
       </c>
     </row>
     <row r="44">
@@ -1875,7 +1875,7 @@
         <v>15.6</v>
       </c>
       <c r="J44">
-        <v>0.45</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="45">
@@ -1913,7 +1913,7 @@
         <v>15.8</v>
       </c>
       <c r="J45">
-        <v>0.59</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="46">
@@ -1951,7 +1951,7 @@
         <v>15.7</v>
       </c>
       <c r="J46">
-        <v>0.5</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="47">
@@ -1989,7 +1989,7 @@
         <v>11.25</v>
       </c>
       <c r="J47">
-        <v>0.48</v>
+        <v>38.15</v>
       </c>
     </row>
     <row r="48">
@@ -2027,7 +2027,7 @@
         <v>11.35</v>
       </c>
       <c r="J48">
-        <v>0.61</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="49">
@@ -2065,7 +2065,7 @@
         <v>11.3</v>
       </c>
       <c r="J49">
-        <v>0.52</v>
+        <v>41.75</v>
       </c>
     </row>
     <row r="50">
@@ -2103,7 +2103,7 @@
         <v>19.3</v>
       </c>
       <c r="J50">
-        <v>0.5</v>
+        <v>40.33</v>
       </c>
     </row>
     <row r="51">
@@ -2141,7 +2141,7 @@
         <v>18.7</v>
       </c>
       <c r="J51">
-        <v>0.66</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="52">
@@ -2179,7 +2179,7 @@
         <v>19</v>
       </c>
       <c r="J52">
-        <v>0.55</v>
+        <v>44.04</v>
       </c>
     </row>
     <row r="53">
@@ -2237,7 +2237,7 @@
         <v>17.3</v>
       </c>
       <c r="J54">
-        <v>0.49</v>
+        <v>39.27</v>
       </c>
     </row>
     <row r="55">
@@ -2295,7 +2295,7 @@
         <v>16.7</v>
       </c>
       <c r="J56">
-        <v>0.62</v>
+        <v>49.93</v>
       </c>
     </row>
     <row r="57">
@@ -2353,7 +2353,7 @@
         <v>17</v>
       </c>
       <c r="J58">
-        <v>0.53</v>
+        <v>42.24</v>
       </c>
     </row>
     <row r="59">
@@ -2411,7 +2411,7 @@
         <v>16.55</v>
       </c>
       <c r="J60">
-        <v>0.51</v>
+        <v>40.77</v>
       </c>
     </row>
     <row r="61">
@@ -2469,7 +2469,7 @@
         <v>16.05</v>
       </c>
       <c r="J62">
-        <v>0.62</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="63">
@@ -2527,7 +2527,7 @@
         <v>16.3</v>
       </c>
       <c r="J64">
-        <v>0.55</v>
+        <v>43.84</v>
       </c>
     </row>
     <row r="65">
@@ -2585,7 +2585,7 @@
         <v>15.95</v>
       </c>
       <c r="J66">
-        <v>0.54</v>
+        <v>43.27</v>
       </c>
     </row>
     <row r="67">
@@ -2643,7 +2643,7 @@
         <v>15.25</v>
       </c>
       <c r="J68">
-        <v>0.67</v>
+        <v>53.36</v>
       </c>
     </row>
     <row r="69">
@@ -2701,7 +2701,7 @@
         <v>15.6</v>
       </c>
       <c r="J70">
-        <v>0.58</v>
+        <v>46.43</v>
       </c>
     </row>
     <row r="71">
@@ -2739,7 +2739,7 @@
         <v>15.4</v>
       </c>
       <c r="J71">
-        <v>0.59</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="72">
@@ -2777,7 +2777,7 @@
         <v>14.72</v>
       </c>
       <c r="J72">
-        <v>0.71</v>
+        <v>56.44</v>
       </c>
     </row>
     <row r="73">
@@ -2815,7 +2815,7 @@
         <v>15.24</v>
       </c>
       <c r="J73">
-        <v>0.62</v>
+        <v>49.96</v>
       </c>
     </row>
     <row r="74">
@@ -2853,7 +2853,7 @@
         <v>15.87</v>
       </c>
       <c r="J74">
-        <v>0.63</v>
+        <v>50.58</v>
       </c>
     </row>
     <row r="75">
@@ -2891,7 +2891,7 @@
         <v>14.19</v>
       </c>
       <c r="J75">
-        <v>0.76</v>
+        <v>60.48</v>
       </c>
     </row>
     <row r="76">
@@ -2929,7 +2929,7 @@
         <v>14.87</v>
       </c>
       <c r="J76">
-        <v>0.67</v>
+        <v>53.54</v>
       </c>
     </row>
     <row r="77">
@@ -2967,7 +2967,7 @@
         <v>15.99</v>
       </c>
       <c r="J77">
-        <v>0.66</v>
+        <v>52.98</v>
       </c>
     </row>
     <row r="78">
@@ -3005,7 +3005,7 @@
         <v>14.03</v>
       </c>
       <c r="J78">
-        <v>0.78</v>
+        <v>62.76</v>
       </c>
     </row>
     <row r="79">
@@ -3043,7 +3043,7 @@
         <v>14.67</v>
       </c>
       <c r="J79">
-        <v>0.7</v>
+        <v>55.82</v>
       </c>
     </row>
     <row r="80">
@@ -3426,7 +3426,7 @@
         <v>3.7</v>
       </c>
       <c r="J92">
-        <v>0.44</v>
+        <v>35.28</v>
       </c>
     </row>
     <row r="93">
@@ -3461,7 +3461,7 @@
         <v>3.1</v>
       </c>
       <c r="J93">
-        <v>0.61</v>
+        <v>48.71</v>
       </c>
     </row>
     <row r="94">
@@ -3496,7 +3496,7 @@
         <v>3.4</v>
       </c>
       <c r="J94">
-        <v>0.5</v>
+        <v>39.84</v>
       </c>
     </row>
     <row r="95">
@@ -3531,7 +3531,7 @@
         <v>3.6</v>
       </c>
       <c r="J95">
-        <v>0.4</v>
+        <v>32.13</v>
       </c>
     </row>
     <row r="96">
@@ -3566,7 +3566,7 @@
         <v>3.2</v>
       </c>
       <c r="J96">
-        <v>0.5600000000000001</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="97">
@@ -3601,7 +3601,7 @@
         <v>3.4</v>
       </c>
       <c r="J97">
-        <v>0.45</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="98">
@@ -3636,7 +3636,7 @@
         <v>5.3</v>
       </c>
       <c r="J98">
-        <v>0.38</v>
+        <v>30.02</v>
       </c>
     </row>
     <row r="99">
@@ -3671,7 +3671,7 @@
         <v>5.7</v>
       </c>
       <c r="J99">
-        <v>0.51</v>
+        <v>40.48</v>
       </c>
     </row>
     <row r="100">
@@ -3706,7 +3706,7 @@
         <v>5.5</v>
       </c>
       <c r="J100">
-        <v>0.42</v>
+        <v>33.98</v>
       </c>
     </row>
     <row r="101">
@@ -3741,7 +3741,7 @@
         <v>5.55</v>
       </c>
       <c r="J101">
-        <v>0.37</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="102">
@@ -3776,7 +3776,7 @@
         <v>5.45</v>
       </c>
       <c r="J102">
-        <v>0.51</v>
+        <v>41.17</v>
       </c>
     </row>
     <row r="103">
@@ -3811,7 +3811,7 @@
         <v>5.5</v>
       </c>
       <c r="J103">
-        <v>0.42</v>
+        <v>33.96</v>
       </c>
     </row>
     <row r="104">
@@ -3846,7 +3846,7 @@
         <v>4.5</v>
       </c>
       <c r="J104">
-        <v>0.36</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="105">
@@ -3881,7 +3881,7 @@
         <v>3.7</v>
       </c>
       <c r="J105">
-        <v>0.51</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="106">
@@ -3916,7 +3916,7 @@
         <v>4.1</v>
       </c>
       <c r="J106">
-        <v>0.42</v>
+        <v>33.53</v>
       </c>
     </row>
     <row r="107">
@@ -3951,7 +3951,7 @@
         <v>11.7</v>
       </c>
       <c r="J107">
-        <v>0.33</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="108">
@@ -3986,7 +3986,7 @@
         <v>11.5</v>
       </c>
       <c r="J108">
-        <v>0.46</v>
+        <v>36.53</v>
       </c>
     </row>
     <row r="109">
@@ -4021,7 +4021,7 @@
         <v>11.6</v>
       </c>
       <c r="J109">
-        <v>0.39</v>
+        <v>30.92</v>
       </c>
     </row>
     <row r="110">
@@ -4059,7 +4059,7 @@
         <v>11</v>
       </c>
       <c r="J110">
-        <v>0.31</v>
+        <v>25.15</v>
       </c>
     </row>
     <row r="111">
@@ -4097,7 +4097,7 @@
         <v>11.2</v>
       </c>
       <c r="J111">
-        <v>0.42</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="112">
@@ -4135,7 +4135,7 @@
         <v>11.1</v>
       </c>
       <c r="J112">
-        <v>0.36</v>
+        <v>28.79</v>
       </c>
     </row>
     <row r="113">
@@ -4173,7 +4173,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J113">
-        <v>0.32</v>
+        <v>25.57</v>
       </c>
     </row>
     <row r="114">
@@ -4211,7 +4211,7 @@
         <v>8</v>
       </c>
       <c r="J114">
-        <v>0.44</v>
+        <v>35.17</v>
       </c>
     </row>
     <row r="115">
@@ -4249,7 +4249,7 @@
         <v>8.1</v>
       </c>
       <c r="J115">
-        <v>0.37</v>
+        <v>29.31</v>
       </c>
     </row>
     <row r="116">
@@ -4287,7 +4287,7 @@
         <v>8.35</v>
       </c>
       <c r="J116">
-        <v>0.34</v>
+        <v>26.85</v>
       </c>
     </row>
     <row r="117">
@@ -4325,7 +4325,7 @@
         <v>8.050000000000001</v>
       </c>
       <c r="J117">
-        <v>0.46</v>
+        <v>36.62</v>
       </c>
     </row>
     <row r="118">
@@ -4363,7 +4363,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J118">
-        <v>0.39</v>
+        <v>30.95</v>
       </c>
     </row>
     <row r="119">
@@ -4401,7 +4401,7 @@
         <v>3.8</v>
       </c>
       <c r="J119">
-        <v>0.35</v>
+        <v>27.72</v>
       </c>
     </row>
     <row r="120">
@@ -4439,7 +4439,7 @@
         <v>3.6</v>
       </c>
       <c r="J120">
-        <v>0.47</v>
+        <v>37.57</v>
       </c>
     </row>
     <row r="121">
@@ -4477,7 +4477,7 @@
         <v>3.7</v>
       </c>
       <c r="J121">
-        <v>0.39</v>
+        <v>31.27</v>
       </c>
     </row>
     <row r="122">
@@ -4515,7 +4515,7 @@
         <v>3.8</v>
       </c>
       <c r="J122">
-        <v>0.36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="123">
@@ -4553,7 +4553,7 @@
         <v>4</v>
       </c>
       <c r="J123">
-        <v>0.49</v>
+        <v>38.96</v>
       </c>
     </row>
     <row r="124">
@@ -4591,7 +4591,7 @@
         <v>3.9</v>
       </c>
       <c r="J124">
-        <v>0.4</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="125">
@@ -4629,7 +4629,7 @@
         <v>3.75</v>
       </c>
       <c r="J125">
-        <v>0.39</v>
+        <v>30.81</v>
       </c>
     </row>
     <row r="126">
@@ -4667,7 +4667,7 @@
         <v>3.85</v>
       </c>
       <c r="J126">
-        <v>0.51</v>
+        <v>40.58</v>
       </c>
     </row>
     <row r="127">
@@ -4705,7 +4705,7 @@
         <v>3.8</v>
       </c>
       <c r="J127">
-        <v>0.43</v>
+        <v>34.66</v>
       </c>
     </row>
     <row r="128">
@@ -4743,7 +4743,7 @@
         <v>5.7</v>
       </c>
       <c r="J128">
-        <v>0.4</v>
+        <v>32.27</v>
       </c>
     </row>
     <row r="129">
@@ -4781,7 +4781,7 @@
         <v>5.1</v>
       </c>
       <c r="J129">
-        <v>0.49</v>
+        <v>39.58</v>
       </c>
     </row>
     <row r="130">
@@ -4819,7 +4819,7 @@
         <v>5.4</v>
       </c>
       <c r="J130">
-        <v>0.44</v>
+        <v>35.08</v>
       </c>
     </row>
     <row r="131">
@@ -4877,7 +4877,7 @@
         <v>12.7</v>
       </c>
       <c r="J132">
-        <v>0.39</v>
+        <v>31.12</v>
       </c>
     </row>
     <row r="133">
@@ -4935,7 +4935,7 @@
         <v>12.1</v>
       </c>
       <c r="J134">
-        <v>0.49</v>
+        <v>39.54</v>
       </c>
     </row>
     <row r="135">
@@ -4993,7 +4993,7 @@
         <v>12.4</v>
       </c>
       <c r="J136">
-        <v>0.43</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="137">
@@ -5051,7 +5051,7 @@
         <v>9.050000000000001</v>
       </c>
       <c r="J138">
-        <v>0.38</v>
+        <v>30.73</v>
       </c>
     </row>
     <row r="139">
@@ -5109,7 +5109,7 @@
         <v>8.550000000000001</v>
       </c>
       <c r="J140">
-        <v>0.5</v>
+        <v>39.71</v>
       </c>
     </row>
     <row r="141">
@@ -5167,7 +5167,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="J142">
-        <v>0.43</v>
+        <v>34.33</v>
       </c>
     </row>
     <row r="143">
@@ -5225,7 +5225,7 @@
         <v>12.25</v>
       </c>
       <c r="J144">
-        <v>0.38</v>
+        <v>30.71</v>
       </c>
     </row>
     <row r="145">
@@ -5283,7 +5283,7 @@
         <v>11.55</v>
       </c>
       <c r="J146">
-        <v>0.5</v>
+        <v>39.65</v>
       </c>
     </row>
     <row r="147">
@@ -5341,7 +5341,7 @@
         <v>11.9</v>
       </c>
       <c r="J148">
-        <v>0.43</v>
+        <v>34.34</v>
       </c>
     </row>
     <row r="149">
@@ -5379,7 +5379,7 @@
         <v>9.880000000000001</v>
       </c>
       <c r="J149">
-        <v>0.4</v>
+        <v>32.22</v>
       </c>
     </row>
     <row r="150">
@@ -5417,7 +5417,7 @@
         <v>10.1</v>
       </c>
       <c r="J150">
-        <v>0.52</v>
+        <v>41.46</v>
       </c>
     </row>
     <row r="151">
@@ -5455,7 +5455,7 @@
         <v>10.02</v>
       </c>
       <c r="J151">
-        <v>0.45</v>
+        <v>36.22</v>
       </c>
     </row>
     <row r="152">
@@ -5493,7 +5493,7 @@
         <v>11.41</v>
       </c>
       <c r="J152">
-        <v>0.43</v>
+        <v>34.71</v>
       </c>
     </row>
     <row r="153">
@@ -5531,7 +5531,7 @@
         <v>10.88</v>
       </c>
       <c r="J153">
-        <v>0.55</v>
+        <v>44.36</v>
       </c>
     </row>
     <row r="154">
@@ -5569,7 +5569,7 @@
         <v>11.24</v>
       </c>
       <c r="J154">
-        <v>0.49</v>
+        <v>38.95</v>
       </c>
     </row>
     <row r="155">
@@ -5607,7 +5607,7 @@
         <v>11.32</v>
       </c>
       <c r="J155">
-        <v>0.46</v>
+        <v>36.83</v>
       </c>
     </row>
     <row r="156">
@@ -5645,7 +5645,7 @@
         <v>10.73</v>
       </c>
       <c r="J156">
-        <v>0.57</v>
+        <v>45.58</v>
       </c>
     </row>
     <row r="157">
@@ -5683,7 +5683,7 @@
         <v>11.05</v>
       </c>
       <c r="J157">
-        <v>0.5</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="158">
@@ -6066,7 +6066,7 @@
         <v>11.3</v>
       </c>
       <c r="J170">
-        <v>0.65</v>
+        <v>52.09</v>
       </c>
     </row>
     <row r="171">
@@ -6101,7 +6101,7 @@
         <v>10.7</v>
       </c>
       <c r="J171">
-        <v>0.73</v>
+        <v>58.11</v>
       </c>
     </row>
     <row r="172">
@@ -6136,7 +6136,7 @@
         <v>11</v>
       </c>
       <c r="J172">
-        <v>0.68</v>
+        <v>54.03</v>
       </c>
     </row>
     <row r="173">
@@ -6171,7 +6171,7 @@
         <v>21</v>
       </c>
       <c r="J173">
-        <v>0.5600000000000001</v>
+        <v>44.92</v>
       </c>
     </row>
     <row r="174">
@@ -6206,7 +6206,7 @@
         <v>20.6</v>
       </c>
       <c r="J174">
-        <v>0.63</v>
+        <v>50.28</v>
       </c>
     </row>
     <row r="175">
@@ -6241,7 +6241,7 @@
         <v>20.8</v>
       </c>
       <c r="J175">
-        <v>0.59</v>
+        <v>46.91</v>
       </c>
     </row>
     <row r="176">
@@ -6276,7 +6276,7 @@
         <v>14.9</v>
       </c>
       <c r="J176">
-        <v>0.53</v>
+        <v>42.33</v>
       </c>
     </row>
     <row r="177">
@@ -6311,7 +6311,7 @@
         <v>15.3</v>
       </c>
       <c r="J177">
-        <v>0.63</v>
+        <v>50.04</v>
       </c>
     </row>
     <row r="178">
@@ -6346,7 +6346,7 @@
         <v>15.1</v>
       </c>
       <c r="J178">
-        <v>0.57</v>
+        <v>45.23</v>
       </c>
     </row>
     <row r="179">
@@ -6381,7 +6381,7 @@
         <v>12.05</v>
       </c>
       <c r="J179">
-        <v>0.48</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="180">
@@ -6416,7 +6416,7 @@
         <v>11.95</v>
       </c>
       <c r="J180">
-        <v>0.58</v>
+        <v>46.16</v>
       </c>
     </row>
     <row r="181">
@@ -6451,7 +6451,7 @@
         <v>12</v>
       </c>
       <c r="J181">
-        <v>0.52</v>
+        <v>41.69</v>
       </c>
     </row>
     <row r="182">
@@ -6486,7 +6486,7 @@
         <v>10.6</v>
       </c>
       <c r="J182">
-        <v>0.45</v>
+        <v>36.28</v>
       </c>
     </row>
     <row r="183">
@@ -6521,7 +6521,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="J183">
-        <v>0.55</v>
+        <v>44.34</v>
       </c>
     </row>
     <row r="184">
@@ -6556,7 +6556,7 @@
         <v>10.2</v>
       </c>
       <c r="J184">
-        <v>0.49</v>
+        <v>39.25</v>
       </c>
     </row>
     <row r="185">
@@ -6591,7 +6591,7 @@
         <v>20.1</v>
       </c>
       <c r="J185">
-        <v>0.44</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="186">
@@ -6626,7 +6626,7 @@
         <v>19.9</v>
       </c>
       <c r="J186">
-        <v>0.52</v>
+        <v>41.35</v>
       </c>
     </row>
     <row r="187">
@@ -6661,7 +6661,7 @@
         <v>20</v>
       </c>
       <c r="J187">
-        <v>0.47</v>
+        <v>37.45</v>
       </c>
     </row>
     <row r="188">
@@ -6699,7 +6699,7 @@
         <v>16.7</v>
       </c>
       <c r="J188">
-        <v>0.45</v>
+        <v>35.89</v>
       </c>
     </row>
     <row r="189">
@@ -6737,7 +6737,7 @@
         <v>16.9</v>
       </c>
       <c r="J189">
-        <v>0.5</v>
+        <v>40.32</v>
       </c>
     </row>
     <row r="190">
@@ -6775,7 +6775,7 @@
         <v>16.8</v>
       </c>
       <c r="J190">
-        <v>0.47</v>
+        <v>37.51</v>
       </c>
     </row>
     <row r="191">
@@ -6813,7 +6813,7 @@
         <v>19</v>
       </c>
       <c r="J191">
-        <v>0.45</v>
+        <v>35.65</v>
       </c>
     </row>
     <row r="192">
@@ -6851,7 +6851,7 @@
         <v>18.8</v>
       </c>
       <c r="J192">
-        <v>0.52</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="193">
@@ -6889,7 +6889,7 @@
         <v>18.9</v>
       </c>
       <c r="J193">
-        <v>0.47</v>
+        <v>37.78</v>
       </c>
     </row>
     <row r="194">
@@ -6927,7 +6927,7 @@
         <v>16.85</v>
       </c>
       <c r="J194">
-        <v>0.48</v>
+        <v>38.54</v>
       </c>
     </row>
     <row r="195">
@@ -6965,7 +6965,7 @@
         <v>16.55</v>
       </c>
       <c r="J195">
-        <v>0.54</v>
+        <v>43.31</v>
       </c>
     </row>
     <row r="196">
@@ -7003,7 +7003,7 @@
         <v>16.7</v>
       </c>
       <c r="J196">
-        <v>0.51</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="197">
@@ -7041,7 +7041,7 @@
         <v>21.2</v>
       </c>
       <c r="J197">
-        <v>0.54</v>
+        <v>43.42</v>
       </c>
     </row>
     <row r="198">
@@ -7079,7 +7079,7 @@
         <v>21</v>
       </c>
       <c r="J198">
-        <v>0.59</v>
+        <v>47.23</v>
       </c>
     </row>
     <row r="199">
@@ -7117,7 +7117,7 @@
         <v>21.1</v>
       </c>
       <c r="J199">
-        <v>0.5600000000000001</v>
+        <v>44.81</v>
       </c>
     </row>
     <row r="200">
@@ -7155,7 +7155,7 @@
         <v>11.8</v>
       </c>
       <c r="J200">
-        <v>0.6</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="201">
@@ -7193,7 +7193,7 @@
         <v>12</v>
       </c>
       <c r="J201">
-        <v>0.6899999999999999</v>
+        <v>55.04</v>
       </c>
     </row>
     <row r="202">
@@ -7231,7 +7231,7 @@
         <v>11.9</v>
       </c>
       <c r="J202">
-        <v>0.64</v>
+        <v>50.88</v>
       </c>
     </row>
     <row r="203">
@@ -7269,7 +7269,7 @@
         <v>9.85</v>
       </c>
       <c r="J203">
-        <v>0.65</v>
+        <v>51.79</v>
       </c>
     </row>
     <row r="204">
@@ -7307,7 +7307,7 @@
         <v>9.949999999999999</v>
       </c>
       <c r="J204">
-        <v>0.72</v>
+        <v>57.84</v>
       </c>
     </row>
     <row r="205">
@@ -7345,7 +7345,7 @@
         <v>9.9</v>
       </c>
       <c r="J205">
-        <v>0.68</v>
+        <v>54.35</v>
       </c>
     </row>
     <row r="206">
@@ -7383,7 +7383,7 @@
         <v>23.3</v>
       </c>
       <c r="J206">
-        <v>0.66</v>
+        <v>52.43</v>
       </c>
     </row>
     <row r="207">
@@ -7421,7 +7421,7 @@
         <v>22.7</v>
       </c>
       <c r="J207">
-        <v>0.7</v>
+        <v>55.77</v>
       </c>
     </row>
     <row r="208">
@@ -7459,7 +7459,7 @@
         <v>23</v>
       </c>
       <c r="J208">
-        <v>0.67</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="209">
@@ -7517,7 +7517,7 @@
         <v>26.5</v>
       </c>
       <c r="J210">
-        <v>0.64</v>
+        <v>50.83</v>
       </c>
     </row>
     <row r="211">
@@ -7575,7 +7575,7 @@
         <v>25.9</v>
       </c>
       <c r="J212">
-        <v>0.6899999999999999</v>
+        <v>55.35</v>
       </c>
     </row>
     <row r="213">
@@ -7633,7 +7633,7 @@
         <v>26.2</v>
       </c>
       <c r="J214">
-        <v>0.65</v>
+        <v>52.23</v>
       </c>
     </row>
     <row r="215">
@@ -7691,7 +7691,7 @@
         <v>20.25</v>
       </c>
       <c r="J216">
-        <v>0.66</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="217">
@@ -7749,7 +7749,7 @@
         <v>19.75</v>
       </c>
       <c r="J218">
-        <v>0.7</v>
+        <v>56.28</v>
       </c>
     </row>
     <row r="219">
@@ -7807,7 +7807,7 @@
         <v>20</v>
       </c>
       <c r="J220">
-        <v>0.68</v>
+        <v>54.41</v>
       </c>
     </row>
     <row r="221">
@@ -7865,7 +7865,7 @@
         <v>21.65</v>
       </c>
       <c r="J222">
-        <v>0.74</v>
+        <v>59.58</v>
       </c>
     </row>
     <row r="223">
@@ -7923,7 +7923,7 @@
         <v>20.95</v>
       </c>
       <c r="J224">
-        <v>0.76</v>
+        <v>61.19</v>
       </c>
     </row>
     <row r="225">
@@ -7981,7 +7981,7 @@
         <v>21.3</v>
       </c>
       <c r="J226">
-        <v>0.75</v>
+        <v>60.06</v>
       </c>
     </row>
     <row r="227">
@@ -8019,7 +8019,7 @@
         <v>17.6</v>
       </c>
       <c r="J227">
-        <v>0.79</v>
+        <v>63.43</v>
       </c>
     </row>
     <row r="228">
@@ -8057,7 +8057,7 @@
         <v>17.93</v>
       </c>
       <c r="J228">
-        <v>0.82</v>
+        <v>65.95</v>
       </c>
     </row>
     <row r="229">
@@ -8095,7 +8095,7 @@
         <v>17.92</v>
       </c>
       <c r="J229">
-        <v>0.8</v>
+        <v>63.89</v>
       </c>
     </row>
     <row r="230">
@@ -8133,7 +8133,7 @@
         <v>18.84</v>
       </c>
       <c r="J230">
-        <v>0.82</v>
+        <v>65.88</v>
       </c>
     </row>
     <row r="231">
@@ -8171,7 +8171,7 @@
         <v>18.81</v>
       </c>
       <c r="J231">
-        <v>0.86</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="232">
@@ -8209,7 +8209,7 @@
         <v>18.8</v>
       </c>
       <c r="J232">
-        <v>0.83</v>
+        <v>66.09</v>
       </c>
     </row>
     <row r="233">
@@ -8247,7 +8247,7 @@
         <v>18.71</v>
       </c>
       <c r="J233">
-        <v>0.84</v>
+        <v>66.92</v>
       </c>
     </row>
     <row r="234">
@@ -8285,7 +8285,7 @@
         <v>18.85</v>
       </c>
       <c r="J234">
-        <v>0.87</v>
+        <v>69.89</v>
       </c>
     </row>
     <row r="235">
@@ -8323,7 +8323,7 @@
         <v>18.85</v>
       </c>
       <c r="J235">
-        <v>0.84</v>
+        <v>67.58</v>
       </c>
     </row>
     <row r="236">
@@ -8706,7 +8706,7 @@
         <v>3.9</v>
       </c>
       <c r="J248">
-        <v>0.71</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="249">
@@ -8741,7 +8741,7 @@
         <v>3.3</v>
       </c>
       <c r="J249">
-        <v>0.92</v>
+        <v>73.70999999999999</v>
       </c>
     </row>
     <row r="250">
@@ -8776,7 +8776,7 @@
         <v>3.6</v>
       </c>
       <c r="J250">
-        <v>0.79</v>
+        <v>62.86</v>
       </c>
     </row>
     <row r="251">
@@ -8811,7 +8811,7 @@
         <v>4.7</v>
       </c>
       <c r="J251">
-        <v>0.57</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="252">
@@ -8846,7 +8846,7 @@
         <v>4.3</v>
       </c>
       <c r="J252">
-        <v>0.79</v>
+        <v>63.46</v>
       </c>
     </row>
     <row r="253">
@@ -8881,7 +8881,7 @@
         <v>4.5</v>
       </c>
       <c r="J253">
-        <v>0.64</v>
+        <v>50.82</v>
       </c>
     </row>
     <row r="254">
@@ -8916,7 +8916,7 @@
         <v>3.2</v>
       </c>
       <c r="J254">
-        <v>0.49</v>
+        <v>39.49</v>
       </c>
     </row>
     <row r="255">
@@ -8951,7 +8951,7 @@
         <v>3.6</v>
       </c>
       <c r="J255">
-        <v>0.68</v>
+        <v>54.63</v>
       </c>
     </row>
     <row r="256">
@@ -8986,7 +8986,7 @@
         <v>3.4</v>
       </c>
       <c r="J256">
-        <v>0.5600000000000001</v>
+        <v>44.78</v>
       </c>
     </row>
     <row r="257">
@@ -9021,7 +9021,7 @@
         <v>9.050000000000001</v>
       </c>
       <c r="J257">
-        <v>0.44</v>
+        <v>35.29</v>
       </c>
     </row>
     <row r="258">
@@ -9056,7 +9056,7 @@
         <v>8.949999999999999</v>
       </c>
       <c r="J258">
-        <v>0.6</v>
+        <v>48.09</v>
       </c>
     </row>
     <row r="259">
@@ -9091,7 +9091,7 @@
         <v>9</v>
       </c>
       <c r="J259">
-        <v>0.5</v>
+        <v>39.79</v>
       </c>
     </row>
     <row r="260">
@@ -9126,7 +9126,7 @@
         <v>3.6</v>
       </c>
       <c r="J260">
-        <v>0.42</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="261">
@@ -9161,7 +9161,7 @@
         <v>2.8</v>
       </c>
       <c r="J261">
-        <v>0.57</v>
+        <v>45.51</v>
       </c>
     </row>
     <row r="262">
@@ -9196,7 +9196,7 @@
         <v>3.2</v>
       </c>
       <c r="J262">
-        <v>0.48</v>
+        <v>38.05</v>
       </c>
     </row>
     <row r="263">
@@ -9231,7 +9231,7 @@
         <v>7.9</v>
       </c>
       <c r="J263">
-        <v>0.37</v>
+        <v>29.57</v>
       </c>
     </row>
     <row r="264">
@@ -9266,7 +9266,7 @@
         <v>7.7</v>
       </c>
       <c r="J264">
-        <v>0.51</v>
+        <v>40.57</v>
       </c>
     </row>
     <row r="265">
@@ -9301,7 +9301,7 @@
         <v>7.8</v>
       </c>
       <c r="J265">
-        <v>0.42</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="266">
@@ -9339,7 +9339,7 @@
         <v>8.1</v>
       </c>
       <c r="J266">
-        <v>0.34</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="267">
@@ -9377,7 +9377,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="J267">
-        <v>0.48</v>
+        <v>38.37</v>
       </c>
     </row>
     <row r="268">
@@ -9415,7 +9415,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J268">
-        <v>0.39</v>
+        <v>31.21</v>
       </c>
     </row>
     <row r="269">
@@ -9453,7 +9453,7 @@
         <v>6.4</v>
       </c>
       <c r="J269">
-        <v>0.34</v>
+        <v>26.88</v>
       </c>
     </row>
     <row r="270">
@@ -9491,7 +9491,7 @@
         <v>6.2</v>
       </c>
       <c r="J270">
-        <v>0.47</v>
+        <v>37.33</v>
       </c>
     </row>
     <row r="271">
@@ -9529,7 +9529,7 @@
         <v>6.3</v>
       </c>
       <c r="J271">
-        <v>0.38</v>
+        <v>30.59</v>
       </c>
     </row>
     <row r="272">
@@ -9567,7 +9567,7 @@
         <v>6.05</v>
       </c>
       <c r="J272">
-        <v>0.37</v>
+        <v>29.88</v>
       </c>
     </row>
     <row r="273">
@@ -9605,7 +9605,7 @@
         <v>5.75</v>
       </c>
       <c r="J273">
-        <v>0.5</v>
+        <v>40.11</v>
       </c>
     </row>
     <row r="274">
@@ -9643,7 +9643,7 @@
         <v>5.9</v>
       </c>
       <c r="J274">
-        <v>0.42</v>
+        <v>33.26</v>
       </c>
     </row>
     <row r="275">
@@ -9681,7 +9681,7 @@
         <v>2.4</v>
       </c>
       <c r="J275">
-        <v>0.38</v>
+        <v>30.57</v>
       </c>
     </row>
     <row r="276">
@@ -9719,7 +9719,7 @@
         <v>2.2</v>
       </c>
       <c r="J276">
-        <v>0.51</v>
+        <v>40.74</v>
       </c>
     </row>
     <row r="277">
@@ -9757,7 +9757,7 @@
         <v>2.3</v>
       </c>
       <c r="J277">
-        <v>0.43</v>
+        <v>34.14</v>
       </c>
     </row>
     <row r="278">
@@ -9795,7 +9795,7 @@
         <v>7</v>
       </c>
       <c r="J278">
-        <v>0.4</v>
+        <v>31.74</v>
       </c>
     </row>
     <row r="279">
@@ -9833,7 +9833,7 @@
         <v>7.2</v>
       </c>
       <c r="J279">
-        <v>0.53</v>
+        <v>42.11</v>
       </c>
     </row>
     <row r="280">
@@ -9871,7 +9871,7 @@
         <v>7.1</v>
       </c>
       <c r="J280">
-        <v>0.45</v>
+        <v>35.99</v>
       </c>
     </row>
     <row r="281">
@@ -9909,7 +9909,7 @@
         <v>3.05</v>
       </c>
       <c r="J281">
-        <v>0.41</v>
+        <v>32.61</v>
       </c>
     </row>
     <row r="282">
@@ -9947,7 +9947,7 @@
         <v>3.15</v>
       </c>
       <c r="J282">
-        <v>0.51</v>
+        <v>40.78</v>
       </c>
     </row>
     <row r="283">
@@ -9985,7 +9985,7 @@
         <v>3.1</v>
       </c>
       <c r="J283">
-        <v>0.44</v>
+        <v>35.03</v>
       </c>
     </row>
     <row r="284">
@@ -10023,7 +10023,7 @@
         <v>7.1</v>
       </c>
       <c r="J284">
-        <v>0.43</v>
+        <v>34.05</v>
       </c>
     </row>
     <row r="285">
@@ -10061,7 +10061,7 @@
         <v>6.5</v>
       </c>
       <c r="J285">
-        <v>0.53</v>
+        <v>42.76</v>
       </c>
     </row>
     <row r="286">
@@ -10099,7 +10099,7 @@
         <v>6.8</v>
       </c>
       <c r="J286">
-        <v>0.46</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="287">
@@ -10157,7 +10157,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="J288">
-        <v>0.42</v>
+        <v>33.94</v>
       </c>
     </row>
     <row r="289">
@@ -10215,7 +10215,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="J290">
-        <v>0.54</v>
+        <v>43.27</v>
       </c>
     </row>
     <row r="291">
@@ -10273,7 +10273,7 @@
         <v>9</v>
       </c>
       <c r="J292">
-        <v>0.47</v>
+        <v>37.39</v>
       </c>
     </row>
     <row r="293">
@@ -10331,7 +10331,7 @@
         <v>5.55</v>
       </c>
       <c r="J294">
-        <v>0.44</v>
+        <v>35.37</v>
       </c>
     </row>
     <row r="295">
@@ -10389,7 +10389,7 @@
         <v>5.05</v>
       </c>
       <c r="J296">
-        <v>0.57</v>
+        <v>45.26</v>
       </c>
     </row>
     <row r="297">
@@ -10447,7 +10447,7 @@
         <v>5.3</v>
       </c>
       <c r="J298">
-        <v>0.49</v>
+        <v>38.81</v>
       </c>
     </row>
     <row r="299">
@@ -10505,7 +10505,7 @@
         <v>7.55</v>
       </c>
       <c r="J300">
-        <v>0.47</v>
+        <v>37.44</v>
       </c>
     </row>
     <row r="301">
@@ -10563,7 +10563,7 @@
         <v>6.85</v>
       </c>
       <c r="J302">
-        <v>0.57</v>
+        <v>45.92</v>
       </c>
     </row>
     <row r="303">
@@ -10621,7 +10621,7 @@
         <v>7.2</v>
       </c>
       <c r="J304">
-        <v>0.51</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="305">
@@ -10659,7 +10659,7 @@
         <v>8.369999999999999</v>
       </c>
       <c r="J305">
-        <v>0.51</v>
+        <v>40.87</v>
       </c>
     </row>
     <row r="306">
@@ -10697,7 +10697,7 @@
         <v>7.99</v>
       </c>
       <c r="J306">
-        <v>0.63</v>
+        <v>50.33</v>
       </c>
     </row>
     <row r="307">
@@ -10735,7 +10735,7 @@
         <v>8.08</v>
       </c>
       <c r="J307">
-        <v>0.55</v>
+        <v>44.21</v>
       </c>
     </row>
     <row r="308">
@@ -10773,7 +10773,7 @@
         <v>7.79</v>
       </c>
       <c r="J308">
-        <v>0.52</v>
+        <v>41.75</v>
       </c>
     </row>
     <row r="309">
@@ -10811,7 +10811,7 @@
         <v>7.33</v>
       </c>
       <c r="J309">
-        <v>0.64</v>
+        <v>51.05</v>
       </c>
     </row>
     <row r="310">
@@ -10849,7 +10849,7 @@
         <v>7.73</v>
       </c>
       <c r="J310">
-        <v>0.57</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="311">
@@ -10887,7 +10887,7 @@
         <v>8.18</v>
       </c>
       <c r="J311">
-        <v>0.52</v>
+        <v>41.38</v>
       </c>
     </row>
     <row r="312">
@@ -10925,7 +10925,7 @@
         <v>7.89</v>
       </c>
       <c r="J312">
-        <v>0.63</v>
+        <v>50.25</v>
       </c>
     </row>
     <row r="313">
@@ -10963,7 +10963,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="J313">
-        <v>0.5600000000000001</v>
+        <v>44.64</v>
       </c>
     </row>
     <row r="314">
@@ -11346,7 +11346,7 @@
         <v>4.3</v>
       </c>
       <c r="J326">
-        <v>0.37</v>
+        <v>29.78</v>
       </c>
     </row>
     <row r="327">
@@ -11381,7 +11381,7 @@
         <v>3.7</v>
       </c>
       <c r="J327">
-        <v>0.47</v>
+        <v>37.51</v>
       </c>
     </row>
     <row r="328">
@@ -11416,7 +11416,7 @@
         <v>4</v>
       </c>
       <c r="J328">
-        <v>0.4</v>
+        <v>32.23</v>
       </c>
     </row>
     <row r="329">
@@ -11451,7 +11451,7 @@
         <v>7.4</v>
       </c>
       <c r="J329">
-        <v>0.33</v>
+        <v>26.64</v>
       </c>
     </row>
     <row r="330">
@@ -11486,7 +11486,7 @@
         <v>7</v>
       </c>
       <c r="J330">
-        <v>0.42</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="331">
@@ -11521,7 +11521,7 @@
         <v>7.2</v>
       </c>
       <c r="J331">
-        <v>0.36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="332">
@@ -11556,7 +11556,7 @@
         <v>9</v>
       </c>
       <c r="J332">
-        <v>0.32</v>
+        <v>25.92</v>
       </c>
     </row>
     <row r="333">
@@ -11591,7 +11591,7 @@
         <v>9.4</v>
       </c>
       <c r="J333">
-        <v>0.42</v>
+        <v>33.56</v>
       </c>
     </row>
     <row r="334">
@@ -11626,7 +11626,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="J334">
-        <v>0.36</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="335">
@@ -11661,7 +11661,7 @@
         <v>7.75</v>
       </c>
       <c r="J335">
-        <v>0.34</v>
+        <v>27.03</v>
       </c>
     </row>
     <row r="336">
@@ -11696,7 +11696,7 @@
         <v>7.65</v>
       </c>
       <c r="J336">
-        <v>0.43</v>
+        <v>34.01</v>
       </c>
     </row>
     <row r="337">
@@ -11731,7 +11731,7 @@
         <v>7.7</v>
       </c>
       <c r="J337">
-        <v>0.37</v>
+        <v>29.91</v>
       </c>
     </row>
     <row r="338">
@@ -11766,7 +11766,7 @@
         <v>7</v>
       </c>
       <c r="J338">
-        <v>0.34</v>
+        <v>27.37</v>
       </c>
     </row>
     <row r="339">
@@ -11801,7 +11801,7 @@
         <v>6.2</v>
       </c>
       <c r="J339">
-        <v>0.44</v>
+        <v>35.26</v>
       </c>
     </row>
     <row r="340">
@@ -11836,7 +11836,7 @@
         <v>6.6</v>
       </c>
       <c r="J340">
-        <v>0.39</v>
+        <v>30.84</v>
       </c>
     </row>
     <row r="341">
@@ -11871,7 +11871,7 @@
         <v>3.3</v>
       </c>
       <c r="J341">
-        <v>0.32</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="342">
@@ -11906,7 +11906,7 @@
         <v>3.1</v>
       </c>
       <c r="J342">
-        <v>0.42</v>
+        <v>33.72</v>
       </c>
     </row>
     <row r="343">
@@ -11941,7 +11941,7 @@
         <v>3.2</v>
       </c>
       <c r="J343">
-        <v>0.36</v>
+        <v>28.98</v>
       </c>
     </row>
     <row r="344">
@@ -11979,7 +11979,7 @@
         <v>4.6</v>
       </c>
       <c r="J344">
-        <v>0.32</v>
+        <v>25.48</v>
       </c>
     </row>
     <row r="345">
@@ -12017,7 +12017,7 @@
         <v>4.8</v>
       </c>
       <c r="J345">
-        <v>0.41</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="346">
@@ -12055,7 +12055,7 @@
         <v>4.7</v>
       </c>
       <c r="J346">
-        <v>0.35</v>
+        <v>28.06</v>
       </c>
     </row>
     <row r="347">
@@ -12093,7 +12093,7 @@
         <v>5.4</v>
       </c>
       <c r="J347">
-        <v>0.31</v>
+        <v>24.48</v>
       </c>
     </row>
     <row r="348">
@@ -12131,7 +12131,7 @@
         <v>5.2</v>
       </c>
       <c r="J348">
-        <v>0.4</v>
+        <v>31.83</v>
       </c>
     </row>
     <row r="349">
@@ -12169,7 +12169,7 @@
         <v>5.3</v>
       </c>
       <c r="J349">
-        <v>0.34</v>
+        <v>27.37</v>
       </c>
     </row>
     <row r="350">
@@ -12207,7 +12207,7 @@
         <v>5.95</v>
       </c>
       <c r="J350">
-        <v>0.31</v>
+        <v>25.12</v>
       </c>
     </row>
     <row r="351">
@@ -12245,7 +12245,7 @@
         <v>5.65</v>
       </c>
       <c r="J351">
-        <v>0.41</v>
+        <v>32.51</v>
       </c>
     </row>
     <row r="352">
@@ -12283,7 +12283,7 @@
         <v>5.8</v>
       </c>
       <c r="J352">
-        <v>0.35</v>
+        <v>27.83</v>
       </c>
     </row>
     <row r="353">
@@ -12321,7 +12321,7 @@
         <v>2.5</v>
       </c>
       <c r="J353">
-        <v>0.32</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="354">
@@ -12359,7 +12359,7 @@
         <v>2.3</v>
       </c>
       <c r="J354">
-        <v>0.43</v>
+        <v>34.29</v>
       </c>
     </row>
     <row r="355">
@@ -12397,7 +12397,7 @@
         <v>2.4</v>
       </c>
       <c r="J355">
-        <v>0.37</v>
+        <v>29.36</v>
       </c>
     </row>
     <row r="356">
@@ -12435,7 +12435,7 @@
         <v>3.1</v>
       </c>
       <c r="J356">
-        <v>0.35</v>
+        <v>27.67</v>
       </c>
     </row>
     <row r="357">
@@ -12473,7 +12473,7 @@
         <v>3.3</v>
       </c>
       <c r="J357">
-        <v>0.43</v>
+        <v>34.74</v>
       </c>
     </row>
     <row r="358">
@@ -12511,7 +12511,7 @@
         <v>3.2</v>
       </c>
       <c r="J358">
-        <v>0.38</v>
+        <v>30.43</v>
       </c>
     </row>
     <row r="359">
@@ -12549,7 +12549,7 @@
         <v>3.05</v>
       </c>
       <c r="J359">
-        <v>0.36</v>
+        <v>29.11</v>
       </c>
     </row>
     <row r="360">
@@ -12587,7 +12587,7 @@
         <v>3.15</v>
       </c>
       <c r="J360">
-        <v>0.47</v>
+        <v>37.46</v>
       </c>
     </row>
     <row r="361">
@@ -12625,7 +12625,7 @@
         <v>3.1</v>
       </c>
       <c r="J361">
-        <v>0.4</v>
+        <v>31.98</v>
       </c>
     </row>
     <row r="362">
@@ -12663,7 +12663,7 @@
         <v>7.2</v>
       </c>
       <c r="J362">
-        <v>0.37</v>
+        <v>29.93</v>
       </c>
     </row>
     <row r="363">
@@ -12701,7 +12701,7 @@
         <v>6.6</v>
       </c>
       <c r="J363">
-        <v>0.47</v>
+        <v>37.78</v>
       </c>
     </row>
     <row r="364">
@@ -12739,7 +12739,7 @@
         <v>6.9</v>
       </c>
       <c r="J364">
-        <v>0.41</v>
+        <v>32.58</v>
       </c>
     </row>
     <row r="365">
@@ -12797,7 +12797,7 @@
         <v>10.3</v>
       </c>
       <c r="J366">
-        <v>0.37</v>
+        <v>29.34</v>
       </c>
     </row>
     <row r="367">
@@ -12855,7 +12855,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="J368">
-        <v>0.47</v>
+        <v>37.73</v>
       </c>
     </row>
     <row r="369">
@@ -12913,7 +12913,7 @@
         <v>10</v>
       </c>
       <c r="J370">
-        <v>0.41</v>
+        <v>32.42</v>
       </c>
     </row>
     <row r="371">
@@ -12971,7 +12971,7 @@
         <v>10.65</v>
       </c>
       <c r="J372">
-        <v>0.38</v>
+        <v>30.01</v>
       </c>
     </row>
     <row r="373">
@@ -13029,7 +13029,7 @@
         <v>10.15</v>
       </c>
       <c r="J374">
-        <v>0.47</v>
+        <v>37.52</v>
       </c>
     </row>
     <row r="375">
@@ -13087,7 +13087,7 @@
         <v>10.4</v>
       </c>
       <c r="J376">
-        <v>0.41</v>
+        <v>32.96</v>
       </c>
     </row>
     <row r="377">
@@ -13145,7 +13145,7 @@
         <v>9.949999999999999</v>
       </c>
       <c r="J378">
-        <v>0.38</v>
+        <v>30.41</v>
       </c>
     </row>
     <row r="379">
@@ -13203,7 +13203,7 @@
         <v>9.25</v>
       </c>
       <c r="J380">
-        <v>0.46</v>
+        <v>36.81</v>
       </c>
     </row>
     <row r="381">
@@ -13261,7 +13261,7 @@
         <v>9.6</v>
       </c>
       <c r="J382">
-        <v>0.41</v>
+        <v>33.17</v>
       </c>
     </row>
     <row r="383">
@@ -13299,7 +13299,7 @@
         <v>10.05</v>
       </c>
       <c r="J383">
-        <v>0.4</v>
+        <v>32.15</v>
       </c>
     </row>
     <row r="384">
@@ -13337,7 +13337,7 @@
         <v>9.43</v>
       </c>
       <c r="J384">
-        <v>0.48</v>
+        <v>38.69</v>
       </c>
     </row>
     <row r="385">
@@ -13375,7 +13375,7 @@
         <v>9.539999999999999</v>
       </c>
       <c r="J385">
-        <v>0.44</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="386">
@@ -13413,7 +13413,7 @@
         <v>10.75</v>
       </c>
       <c r="J386">
-        <v>0.43</v>
+        <v>34.19</v>
       </c>
     </row>
     <row r="387">
@@ -13451,7 +13451,7 @@
         <v>9.32</v>
       </c>
       <c r="J387">
-        <v>0.52</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="388">
@@ -13489,7 +13489,7 @@
         <v>9.710000000000001</v>
       </c>
       <c r="J388">
-        <v>0.46</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="389">
@@ -13527,7 +13527,7 @@
         <v>10.69</v>
       </c>
       <c r="J389">
-        <v>0.44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="390">
@@ -13565,7 +13565,7 @@
         <v>9.619999999999999</v>
       </c>
       <c r="J390">
-        <v>0.53</v>
+        <v>42.14</v>
       </c>
     </row>
     <row r="391">
@@ -13603,7 +13603,7 @@
         <v>10.39</v>
       </c>
       <c r="J391">
-        <v>0.48</v>
+        <v>38.29</v>
       </c>
     </row>
     <row r="392">
@@ -13986,7 +13986,7 @@
         <v>10</v>
       </c>
       <c r="J404">
-        <v>0.38</v>
+        <v>30.52</v>
       </c>
     </row>
     <row r="405">
@@ -14021,7 +14021,7 @@
         <v>9.4</v>
       </c>
       <c r="J405">
-        <v>0.45</v>
+        <v>35.79</v>
       </c>
     </row>
     <row r="406">
@@ -14056,7 +14056,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="J406">
-        <v>0.4</v>
+        <v>32.13</v>
       </c>
     </row>
     <row r="407">
@@ -14091,7 +14091,7 @@
         <v>12.6</v>
       </c>
       <c r="J407">
-        <v>0.35</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="408">
@@ -14126,7 +14126,7 @@
         <v>12.2</v>
       </c>
       <c r="J408">
-        <v>0.42</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="409">
@@ -14161,7 +14161,7 @@
         <v>12.4</v>
       </c>
       <c r="J409">
-        <v>0.37</v>
+        <v>29.64</v>
       </c>
     </row>
     <row r="410">
@@ -14196,7 +14196,7 @@
         <v>9</v>
       </c>
       <c r="J410">
-        <v>0.33</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="411">
@@ -14231,7 +14231,7 @@
         <v>9.4</v>
       </c>
       <c r="J411">
-        <v>0.4</v>
+        <v>32.32</v>
       </c>
     </row>
     <row r="412">
@@ -14266,7 +14266,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="J412">
-        <v>0.35</v>
+        <v>28.01</v>
       </c>
     </row>
     <row r="413">
@@ -14301,7 +14301,7 @@
         <v>9.050000000000001</v>
       </c>
       <c r="J413">
-        <v>0.32</v>
+        <v>25.77</v>
       </c>
     </row>
     <row r="414">
@@ -14336,7 +14336,7 @@
         <v>8.949999999999999</v>
       </c>
       <c r="J414">
-        <v>0.38</v>
+        <v>30.66</v>
       </c>
     </row>
     <row r="415">
@@ -14371,7 +14371,7 @@
         <v>9</v>
       </c>
       <c r="J415">
-        <v>0.35</v>
+        <v>27.64</v>
       </c>
     </row>
     <row r="416">
@@ -14406,7 +14406,7 @@
         <v>8.9</v>
       </c>
       <c r="J416">
-        <v>0.32</v>
+        <v>25.92</v>
       </c>
     </row>
     <row r="417">
@@ -14441,7 +14441,7 @@
         <v>8.1</v>
       </c>
       <c r="J417">
-        <v>0.41</v>
+        <v>32.54</v>
       </c>
     </row>
     <row r="418">
@@ -14476,7 +14476,7 @@
         <v>8.5</v>
       </c>
       <c r="J418">
-        <v>0.35</v>
+        <v>28.13</v>
       </c>
     </row>
     <row r="419">
@@ -14511,7 +14511,7 @@
         <v>15.6</v>
       </c>
       <c r="J419">
-        <v>0.29</v>
+        <v>23.55</v>
       </c>
     </row>
     <row r="420">
@@ -14546,7 +14546,7 @@
         <v>15.4</v>
       </c>
       <c r="J420">
-        <v>0.37</v>
+        <v>29.73</v>
       </c>
     </row>
     <row r="421">
@@ -14581,7 +14581,7 @@
         <v>15.5</v>
       </c>
       <c r="J421">
-        <v>0.32</v>
+        <v>25.92</v>
       </c>
     </row>
     <row r="422">
@@ -14619,7 +14619,7 @@
         <v>13.4</v>
       </c>
       <c r="J422">
-        <v>0.28</v>
+        <v>22.42</v>
       </c>
     </row>
     <row r="423">
@@ -14657,7 +14657,7 @@
         <v>13.6</v>
       </c>
       <c r="J423">
-        <v>0.34</v>
+        <v>27.06</v>
       </c>
     </row>
     <row r="424">
@@ -14695,7 +14695,7 @@
         <v>13.5</v>
       </c>
       <c r="J424">
-        <v>0.3</v>
+        <v>23.96</v>
       </c>
     </row>
     <row r="425">
@@ -14733,7 +14733,7 @@
         <v>13.2</v>
       </c>
       <c r="J425">
-        <v>0.28</v>
+        <v>22.23</v>
       </c>
     </row>
     <row r="426">
@@ -14771,7 +14771,7 @@
         <v>13</v>
       </c>
       <c r="J426">
-        <v>0.34</v>
+        <v>27.57</v>
       </c>
     </row>
     <row r="427">
@@ -14809,7 +14809,7 @@
         <v>13.1</v>
       </c>
       <c r="J427">
-        <v>0.3</v>
+        <v>24.19</v>
       </c>
     </row>
     <row r="428">
@@ -14847,7 +14847,7 @@
         <v>16.75</v>
       </c>
       <c r="J428">
-        <v>0.28</v>
+        <v>22.74</v>
       </c>
     </row>
     <row r="429">
@@ -14885,7 +14885,7 @@
         <v>16.45</v>
       </c>
       <c r="J429">
-        <v>0.35</v>
+        <v>28.12</v>
       </c>
     </row>
     <row r="430">
@@ -14923,7 +14923,7 @@
         <v>16.6</v>
       </c>
       <c r="J430">
-        <v>0.31</v>
+        <v>24.65</v>
       </c>
     </row>
     <row r="431">
@@ -14961,7 +14961,7 @@
         <v>5</v>
       </c>
       <c r="J431">
-        <v>0.3</v>
+        <v>23.63</v>
       </c>
     </row>
     <row r="432">
@@ -14999,7 +14999,7 @@
         <v>4.8</v>
       </c>
       <c r="J432">
-        <v>0.38</v>
+        <v>30.14</v>
       </c>
     </row>
     <row r="433">
@@ -15037,7 +15037,7 @@
         <v>4.9</v>
       </c>
       <c r="J433">
-        <v>0.32</v>
+        <v>25.71</v>
       </c>
     </row>
     <row r="434">
@@ -15075,7 +15075,7 @@
         <v>9</v>
       </c>
       <c r="J434">
-        <v>0.3</v>
+        <v>24.14</v>
       </c>
     </row>
     <row r="435">
@@ -15113,7 +15113,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="J435">
-        <v>0.38</v>
+        <v>30.72</v>
       </c>
     </row>
     <row r="436">
@@ -15151,7 +15151,7 @@
         <v>9.1</v>
       </c>
       <c r="J436">
-        <v>0.33</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="437">
@@ -15189,7 +15189,7 @@
         <v>6.15</v>
       </c>
       <c r="J437">
-        <v>0.32</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="438">
@@ -15227,7 +15227,7 @@
         <v>6.25</v>
       </c>
       <c r="J438">
-        <v>0.38</v>
+        <v>30.79</v>
       </c>
     </row>
     <row r="439">
@@ -15265,7 +15265,7 @@
         <v>6.2</v>
       </c>
       <c r="J439">
-        <v>0.34</v>
+        <v>27.38</v>
       </c>
     </row>
     <row r="440">
@@ -15303,7 +15303,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="J440">
-        <v>0.33</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="441">
@@ -15341,7 +15341,7 @@
         <v>8.1</v>
       </c>
       <c r="J441">
-        <v>0.39</v>
+        <v>31.27</v>
       </c>
     </row>
     <row r="442">
@@ -15379,7 +15379,7 @@
         <v>8.4</v>
       </c>
       <c r="J442">
-        <v>0.35</v>
+        <v>28.05</v>
       </c>
     </row>
     <row r="443">
@@ -15437,7 +15437,7 @@
         <v>14.5</v>
       </c>
       <c r="J444">
-        <v>0.33</v>
+        <v>26.74</v>
       </c>
     </row>
     <row r="445">
@@ -15495,7 +15495,7 @@
         <v>13.9</v>
       </c>
       <c r="J446">
-        <v>0.4</v>
+        <v>31.89</v>
       </c>
     </row>
     <row r="447">
@@ -15553,7 +15553,7 @@
         <v>14.2</v>
       </c>
       <c r="J448">
-        <v>0.36</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="449">
@@ -15611,7 +15611,7 @@
         <v>14.75</v>
       </c>
       <c r="J450">
-        <v>0.33</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="451">
@@ -15669,7 +15669,7 @@
         <v>14.25</v>
       </c>
       <c r="J452">
-        <v>0.41</v>
+        <v>32.85</v>
       </c>
     </row>
     <row r="453">
@@ -15727,7 +15727,7 @@
         <v>14.5</v>
       </c>
       <c r="J454">
-        <v>0.36</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="455">
@@ -15785,7 +15785,7 @@
         <v>13.45</v>
       </c>
       <c r="J456">
-        <v>0.34</v>
+        <v>27.52</v>
       </c>
     </row>
     <row r="457">
@@ -15843,7 +15843,7 @@
         <v>12.75</v>
       </c>
       <c r="J458">
-        <v>0.41</v>
+        <v>33.17</v>
       </c>
     </row>
     <row r="459">
@@ -15901,7 +15901,7 @@
         <v>13.1</v>
       </c>
       <c r="J460">
-        <v>0.37</v>
+        <v>29.52</v>
       </c>
     </row>
     <row r="461">
@@ -15939,7 +15939,7 @@
         <v>13.85</v>
       </c>
       <c r="J461">
-        <v>0.36</v>
+        <v>28.92</v>
       </c>
     </row>
     <row r="462">
@@ -15977,7 +15977,7 @@
         <v>12.94</v>
       </c>
       <c r="J462">
-        <v>0.43</v>
+        <v>34.12</v>
       </c>
     </row>
     <row r="463">
@@ -16015,7 +16015,7 @@
         <v>13.69</v>
       </c>
       <c r="J463">
-        <v>0.39</v>
+        <v>31.21</v>
       </c>
     </row>
     <row r="464">
@@ -16053,7 +16053,7 @@
         <v>13.87</v>
       </c>
       <c r="J464">
-        <v>0.39</v>
+        <v>31.38</v>
       </c>
     </row>
     <row r="465">
@@ -16091,7 +16091,7 @@
         <v>12.71</v>
       </c>
       <c r="J465">
-        <v>0.46</v>
+        <v>36.81</v>
       </c>
     </row>
     <row r="466">
@@ -16129,7 +16129,7 @@
         <v>13.36</v>
       </c>
       <c r="J466">
-        <v>0.42</v>
+        <v>33.36</v>
       </c>
     </row>
     <row r="467">
@@ -16167,7 +16167,7 @@
         <v>13.69</v>
       </c>
       <c r="J467">
-        <v>0.42</v>
+        <v>33.52</v>
       </c>
     </row>
     <row r="468">
@@ -16205,7 +16205,7 @@
         <v>13.05</v>
       </c>
       <c r="J468">
-        <v>0.48</v>
+        <v>38.68</v>
       </c>
     </row>
     <row r="469">
@@ -16243,7 +16243,7 @@
         <v>13.53</v>
       </c>
       <c r="J469">
-        <v>0.44</v>
+        <v>35.29</v>
       </c>
     </row>
     <row r="470">
@@ -16626,7 +16626,7 @@
         <v>8.9</v>
       </c>
       <c r="J482">
-        <v>0.57</v>
+        <v>45.36</v>
       </c>
     </row>
     <row r="483">
@@ -16661,7 +16661,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="J483">
-        <v>0.75</v>
+        <v>60.15</v>
       </c>
     </row>
     <row r="484">
@@ -16696,7 +16696,7 @@
         <v>8.6</v>
       </c>
       <c r="J484">
-        <v>0.64</v>
+        <v>51.22</v>
       </c>
     </row>
     <row r="485">
@@ -16731,7 +16731,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="J485">
-        <v>0.51</v>
+        <v>40.52</v>
       </c>
     </row>
     <row r="486">
@@ -16766,7 +16766,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="J486">
-        <v>0.67</v>
+        <v>53.31</v>
       </c>
     </row>
     <row r="487">
@@ -16801,7 +16801,7 @@
         <v>9</v>
       </c>
       <c r="J487">
-        <v>0.57</v>
+        <v>45.55</v>
       </c>
     </row>
     <row r="488">
@@ -16836,7 +16836,7 @@
         <v>11.9</v>
       </c>
       <c r="J488">
-        <v>0.5</v>
+        <v>39.85</v>
       </c>
     </row>
     <row r="489">
@@ -16871,7 +16871,7 @@
         <v>12.3</v>
       </c>
       <c r="J489">
-        <v>0.65</v>
+        <v>51.95</v>
       </c>
     </row>
     <row r="490">
@@ -16906,7 +16906,7 @@
         <v>12.1</v>
       </c>
       <c r="J490">
-        <v>0.5600000000000001</v>
+        <v>44.89</v>
       </c>
     </row>
     <row r="491">
@@ -16941,7 +16941,7 @@
         <v>6.55</v>
       </c>
       <c r="J491">
-        <v>0.49</v>
+        <v>39.05</v>
       </c>
     </row>
     <row r="492">
@@ -16976,7 +16976,7 @@
         <v>6.45</v>
       </c>
       <c r="J492">
-        <v>0.65</v>
+        <v>51.67</v>
       </c>
     </row>
     <row r="493">
@@ -17011,7 +17011,7 @@
         <v>6.5</v>
       </c>
       <c r="J493">
-        <v>0.55</v>
+        <v>44.27</v>
       </c>
     </row>
     <row r="494">
@@ -17046,7 +17046,7 @@
         <v>13.4</v>
       </c>
       <c r="J494">
-        <v>0.47</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="495">
@@ -17081,7 +17081,7 @@
         <v>12.6</v>
       </c>
       <c r="J495">
-        <v>0.63</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="496">
@@ -17116,7 +17116,7 @@
         <v>13</v>
       </c>
       <c r="J496">
-        <v>0.54</v>
+        <v>43.22</v>
       </c>
     </row>
     <row r="497">
@@ -17151,7 +17151,7 @@
         <v>10.7</v>
       </c>
       <c r="J497">
-        <v>0.44</v>
+        <v>35.23</v>
       </c>
     </row>
     <row r="498">
@@ -17186,7 +17186,7 @@
         <v>10.5</v>
       </c>
       <c r="J498">
-        <v>0.59</v>
+        <v>46.93</v>
       </c>
     </row>
     <row r="499">
@@ -17221,7 +17221,7 @@
         <v>10.6</v>
       </c>
       <c r="J499">
-        <v>0.51</v>
+        <v>40.59</v>
       </c>
     </row>
     <row r="500">
@@ -17259,7 +17259,7 @@
         <v>10.4</v>
       </c>
       <c r="J500">
-        <v>0.44</v>
+        <v>35.46</v>
       </c>
     </row>
     <row r="501">
@@ -17297,7 +17297,7 @@
         <v>10.6</v>
       </c>
       <c r="J501">
-        <v>0.59</v>
+        <v>46.81</v>
       </c>
     </row>
     <row r="502">
@@ -17335,7 +17335,7 @@
         <v>10.5</v>
       </c>
       <c r="J502">
-        <v>0.51</v>
+        <v>40.82</v>
       </c>
     </row>
     <row r="503">
@@ -17373,7 +17373,7 @@
         <v>12</v>
       </c>
       <c r="J503">
-        <v>0.49</v>
+        <v>38.86</v>
       </c>
     </row>
     <row r="504">
@@ -17411,7 +17411,7 @@
         <v>11.8</v>
       </c>
       <c r="J504">
-        <v>0.64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="505">
@@ -17449,7 +17449,7 @@
         <v>11.9</v>
       </c>
       <c r="J505">
-        <v>0.55</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="506">
@@ -17487,7 +17487,7 @@
         <v>10.05</v>
       </c>
       <c r="J506">
-        <v>0.54</v>
+        <v>43.23</v>
       </c>
     </row>
     <row r="507">
@@ -17525,7 +17525,7 @@
         <v>9.75</v>
       </c>
       <c r="J507">
-        <v>0.71</v>
+        <v>56.59</v>
       </c>
     </row>
     <row r="508">
@@ -17563,7 +17563,7 @@
         <v>9.9</v>
       </c>
       <c r="J508">
-        <v>0.61</v>
+        <v>49.07</v>
       </c>
     </row>
     <row r="509">
@@ -17601,7 +17601,7 @@
         <v>8.4</v>
       </c>
       <c r="J509">
-        <v>0.62</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="510">
@@ -17639,7 +17639,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J510">
-        <v>0.8</v>
+        <v>63.91</v>
       </c>
     </row>
     <row r="511">
@@ -17677,7 +17677,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="J511">
-        <v>0.6899999999999999</v>
+        <v>55.51</v>
       </c>
     </row>
     <row r="512">
@@ -17715,7 +17715,7 @@
         <v>8.6</v>
       </c>
       <c r="J512">
-        <v>0.64</v>
+        <v>51.38</v>
       </c>
     </row>
     <row r="513">
@@ -17753,7 +17753,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="J513">
-        <v>0.84</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="514">
@@ -17791,7 +17791,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="J514">
-        <v>0.72</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="515">
@@ -17829,7 +17829,7 @@
         <v>8.050000000000001</v>
       </c>
       <c r="J515">
-        <v>0.66</v>
+        <v>52.58</v>
       </c>
     </row>
     <row r="516">
@@ -17867,7 +17867,7 @@
         <v>8.15</v>
       </c>
       <c r="J516">
-        <v>0.82</v>
+        <v>65.95999999999999</v>
       </c>
     </row>
     <row r="517">
@@ -17905,7 +17905,7 @@
         <v>8.1</v>
       </c>
       <c r="J517">
-        <v>0.73</v>
+        <v>58.37</v>
       </c>
     </row>
     <row r="518">
@@ -17943,7 +17943,7 @@
         <v>14.6</v>
       </c>
       <c r="J518">
-        <v>0.65</v>
+        <v>52.26</v>
       </c>
     </row>
     <row r="519">
@@ -17981,7 +17981,7 @@
         <v>14</v>
       </c>
       <c r="J519">
-        <v>0.82</v>
+        <v>65.41</v>
       </c>
     </row>
     <row r="520">
@@ -18019,7 +18019,7 @@
         <v>14.3</v>
       </c>
       <c r="J520">
-        <v>0.72</v>
+        <v>57.52</v>
       </c>
     </row>
     <row r="521">
@@ -18077,7 +18077,7 @@
         <v>14.5</v>
       </c>
       <c r="J522">
-        <v>0.59</v>
+        <v>47.24</v>
       </c>
     </row>
     <row r="523">
@@ -18135,7 +18135,7 @@
         <v>13.9</v>
       </c>
       <c r="J524">
-        <v>0.74</v>
+        <v>59.32</v>
       </c>
     </row>
     <row r="525">
@@ -18193,7 +18193,7 @@
         <v>14.2</v>
       </c>
       <c r="J526">
-        <v>0.65</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="527">
@@ -18251,7 +18251,7 @@
         <v>15.05</v>
       </c>
       <c r="J528">
-        <v>0.6</v>
+        <v>48.05</v>
       </c>
     </row>
     <row r="529">
@@ -18309,7 +18309,7 @@
         <v>14.55</v>
       </c>
       <c r="J530">
-        <v>0.76</v>
+        <v>60.97</v>
       </c>
     </row>
     <row r="531">
@@ -18367,7 +18367,7 @@
         <v>14.8</v>
       </c>
       <c r="J532">
-        <v>0.66</v>
+        <v>53.17</v>
       </c>
     </row>
     <row r="533">
@@ -18425,7 +18425,7 @@
         <v>14.35</v>
       </c>
       <c r="J534">
-        <v>0.66</v>
+        <v>52.72</v>
       </c>
     </row>
     <row r="535">
@@ -18483,7 +18483,7 @@
         <v>13.65</v>
       </c>
       <c r="J536">
-        <v>0.79</v>
+        <v>63</v>
       </c>
     </row>
     <row r="537">
@@ -18541,7 +18541,7 @@
         <v>14</v>
       </c>
       <c r="J538">
-        <v>0.71</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="539">
@@ -18579,7 +18579,7 @@
         <v>14.27</v>
       </c>
       <c r="J539">
-        <v>0.72</v>
+        <v>57.93</v>
       </c>
     </row>
     <row r="540">
@@ -18617,7 +18617,7 @@
         <v>13.95</v>
       </c>
       <c r="J540">
-        <v>0.87</v>
+        <v>69.53</v>
       </c>
     </row>
     <row r="541">
@@ -18655,7 +18655,7 @@
         <v>14.12</v>
       </c>
       <c r="J541">
-        <v>0.78</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="542">
@@ -18693,7 +18693,7 @@
         <v>14.04</v>
       </c>
       <c r="J542">
-        <v>0.77</v>
+        <v>61.92</v>
       </c>
     </row>
     <row r="543">
@@ -18731,7 +18731,7 @@
         <v>13.85</v>
       </c>
       <c r="J543">
-        <v>0.92</v>
+        <v>73.55</v>
       </c>
     </row>
     <row r="544">
@@ -18769,7 +18769,7 @@
         <v>14.03</v>
       </c>
       <c r="J544">
-        <v>0.83</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="545">
@@ -18807,7 +18807,7 @@
         <v>13.99</v>
       </c>
       <c r="J545">
-        <v>0.72</v>
+        <v>57.36</v>
       </c>
     </row>
     <row r="546">
@@ -18845,7 +18845,7 @@
         <v>14</v>
       </c>
       <c r="J546">
-        <v>0.85</v>
+        <v>67.73999999999999</v>
       </c>
     </row>
     <row r="547">
@@ -18883,7 +18883,7 @@
         <v>14</v>
       </c>
       <c r="J547">
-        <v>0.77</v>
+        <v>61.64</v>
       </c>
     </row>
     <row r="548">
@@ -19458,7 +19458,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="J566">
-        <v>0.32</v>
+        <v>25.61</v>
       </c>
     </row>
     <row r="567">
@@ -19493,7 +19493,7 @@
         <v>10.1</v>
       </c>
       <c r="J567">
-        <v>0.43</v>
+        <v>34.78</v>
       </c>
     </row>
     <row r="568">
@@ -19528,7 +19528,7 @@
         <v>9.9</v>
       </c>
       <c r="J568">
-        <v>0.37</v>
+        <v>29.24</v>
       </c>
     </row>
     <row r="569">
@@ -19563,7 +19563,7 @@
         <v>7.65</v>
       </c>
       <c r="J569">
-        <v>0.33</v>
+        <v>26.24</v>
       </c>
     </row>
     <row r="570">
@@ -19598,7 +19598,7 @@
         <v>7.55</v>
       </c>
       <c r="J570">
-        <v>0.46</v>
+        <v>36.73</v>
       </c>
     </row>
     <row r="571">
@@ -19633,7 +19633,7 @@
         <v>7.6</v>
       </c>
       <c r="J571">
-        <v>0.38</v>
+        <v>30.15</v>
       </c>
     </row>
     <row r="572">
@@ -19668,7 +19668,7 @@
         <v>5.9</v>
       </c>
       <c r="J572">
-        <v>0.34</v>
+        <v>27.51</v>
       </c>
     </row>
     <row r="573">
@@ -19703,7 +19703,7 @@
         <v>5.1</v>
       </c>
       <c r="J573">
-        <v>0.49</v>
+        <v>39.25</v>
       </c>
     </row>
     <row r="574">
@@ -19738,7 +19738,7 @@
         <v>5.5</v>
       </c>
       <c r="J574">
-        <v>0.41</v>
+        <v>32.54</v>
       </c>
     </row>
     <row r="575">
@@ -19773,7 +19773,7 @@
         <v>3.4</v>
       </c>
       <c r="J575">
-        <v>0.3</v>
+        <v>24.32</v>
       </c>
     </row>
     <row r="576">
@@ -19808,7 +19808,7 @@
         <v>3.2</v>
       </c>
       <c r="J576">
-        <v>0.44</v>
+        <v>35.43</v>
       </c>
     </row>
     <row r="577">
@@ -19843,7 +19843,7 @@
         <v>3.3</v>
       </c>
       <c r="J577">
-        <v>0.37</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="578">
@@ -19881,7 +19881,7 @@
         <v>6.2</v>
       </c>
       <c r="J578">
-        <v>0.29</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="579">
@@ -19919,7 +19919,7 @@
         <v>6.4</v>
       </c>
       <c r="J579">
-        <v>0.42</v>
+        <v>33.72</v>
       </c>
     </row>
     <row r="580">
@@ -19957,7 +19957,7 @@
         <v>6.3</v>
       </c>
       <c r="J580">
-        <v>0.34</v>
+        <v>27.34</v>
       </c>
     </row>
     <row r="581">
@@ -19995,7 +19995,7 @@
         <v>6</v>
       </c>
       <c r="J581">
-        <v>0.29</v>
+        <v>23.36</v>
       </c>
     </row>
     <row r="582">
@@ -20033,7 +20033,7 @@
         <v>5.8</v>
       </c>
       <c r="J582">
-        <v>0.41</v>
+        <v>32.83</v>
       </c>
     </row>
     <row r="583">
@@ -20071,7 +20071,7 @@
         <v>5.9</v>
       </c>
       <c r="J583">
-        <v>0.34</v>
+        <v>27.23</v>
       </c>
     </row>
     <row r="584">
@@ -20109,7 +20109,7 @@
         <v>5.65</v>
       </c>
       <c r="J584">
-        <v>0.3</v>
+        <v>24.07</v>
       </c>
     </row>
     <row r="585">
@@ -20147,7 +20147,7 @@
         <v>5.35</v>
       </c>
       <c r="J585">
-        <v>0.42</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="586">
@@ -20185,7 +20185,7 @@
         <v>5.5</v>
       </c>
       <c r="J586">
-        <v>0.35</v>
+        <v>28.06</v>
       </c>
     </row>
     <row r="587">
@@ -20223,7 +20223,7 @@
         <v>2.3</v>
       </c>
       <c r="J587">
-        <v>0.31</v>
+        <v>24.69</v>
       </c>
     </row>
     <row r="588">
@@ -20261,7 +20261,7 @@
         <v>2.1</v>
       </c>
       <c r="J588">
-        <v>0.42</v>
+        <v>33.51</v>
       </c>
     </row>
     <row r="589">
@@ -20299,7 +20299,7 @@
         <v>2.2</v>
       </c>
       <c r="J589">
-        <v>0.35</v>
+        <v>28.21</v>
       </c>
     </row>
     <row r="590">
@@ -20337,7 +20337,7 @@
         <v>10.2</v>
       </c>
       <c r="J590">
-        <v>0.33</v>
+        <v>26.61</v>
       </c>
     </row>
     <row r="591">
@@ -20375,7 +20375,7 @@
         <v>10.4</v>
       </c>
       <c r="J591">
-        <v>0.43</v>
+        <v>34.79</v>
       </c>
     </row>
     <row r="592">
@@ -20413,7 +20413,7 @@
         <v>10.3</v>
       </c>
       <c r="J592">
-        <v>0.38</v>
+        <v>30.26</v>
       </c>
     </row>
     <row r="593">
@@ -20451,7 +20451,7 @@
         <v>6.85</v>
       </c>
       <c r="J593">
-        <v>0.35</v>
+        <v>28.21</v>
       </c>
     </row>
     <row r="594">
@@ -20489,7 +20489,7 @@
         <v>6.95</v>
       </c>
       <c r="J594">
-        <v>0.44</v>
+        <v>35.05</v>
       </c>
     </row>
     <row r="595">
@@ -20527,7 +20527,7 @@
         <v>6.9</v>
       </c>
       <c r="J595">
-        <v>0.39</v>
+        <v>30.82</v>
       </c>
     </row>
     <row r="596">
@@ -20565,7 +20565,7 @@
         <v>11.7</v>
       </c>
       <c r="J596">
-        <v>0.37</v>
+        <v>29.36</v>
       </c>
     </row>
     <row r="597">
@@ -20603,7 +20603,7 @@
         <v>11.1</v>
       </c>
       <c r="J597">
-        <v>0.47</v>
+        <v>37.28</v>
       </c>
     </row>
     <row r="598">
@@ -20641,7 +20641,7 @@
         <v>11.4</v>
       </c>
       <c r="J598">
-        <v>0.4</v>
+        <v>32.33</v>
       </c>
     </row>
     <row r="599">
@@ -20699,7 +20699,7 @@
         <v>10.6</v>
       </c>
       <c r="J600">
-        <v>0.38</v>
+        <v>30.32</v>
       </c>
     </row>
     <row r="601">
@@ -20757,7 +20757,7 @@
         <v>10</v>
       </c>
       <c r="J602">
-        <v>0.48</v>
+        <v>38.05</v>
       </c>
     </row>
     <row r="603">
@@ -20815,7 +20815,7 @@
         <v>10.3</v>
       </c>
       <c r="J604">
-        <v>0.42</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="605">
@@ -20873,7 +20873,7 @@
         <v>11.05</v>
       </c>
       <c r="J606">
-        <v>0.38</v>
+        <v>30.79</v>
       </c>
     </row>
     <row r="607">
@@ -20931,7 +20931,7 @@
         <v>10.55</v>
       </c>
       <c r="J608">
-        <v>0.47</v>
+        <v>37.77</v>
       </c>
     </row>
     <row r="609">
@@ -20989,7 +20989,7 @@
         <v>10.8</v>
       </c>
       <c r="J610">
-        <v>0.42</v>
+        <v>33.68</v>
       </c>
     </row>
     <row r="611">
@@ -21047,7 +21047,7 @@
         <v>12.25</v>
       </c>
       <c r="J612">
-        <v>0.37</v>
+        <v>29.96</v>
       </c>
     </row>
     <row r="613">
@@ -21105,7 +21105,7 @@
         <v>11.55</v>
       </c>
       <c r="J614">
-        <v>0.47</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="615">
@@ -21163,7 +21163,7 @@
         <v>11.9</v>
       </c>
       <c r="J616">
-        <v>0.41</v>
+        <v>32.78</v>
       </c>
     </row>
     <row r="617">
@@ -21201,7 +21201,7 @@
         <v>11.89</v>
       </c>
       <c r="J617">
-        <v>0.4</v>
+        <v>32.16</v>
       </c>
     </row>
     <row r="618">
@@ -21239,7 +21239,7 @@
         <v>11.85</v>
       </c>
       <c r="J618">
-        <v>0.48</v>
+        <v>38.39</v>
       </c>
     </row>
     <row r="619">
@@ -21277,7 +21277,7 @@
         <v>11.83</v>
       </c>
       <c r="J619">
-        <v>0.44</v>
+        <v>34.81</v>
       </c>
     </row>
     <row r="620">
@@ -21315,7 +21315,7 @@
         <v>12.11</v>
       </c>
       <c r="J620">
-        <v>0.42</v>
+        <v>33.39</v>
       </c>
     </row>
     <row r="621">
@@ -21353,7 +21353,7 @@
         <v>11.95</v>
       </c>
       <c r="J621">
-        <v>0.49</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="622">
@@ -21391,7 +21391,7 @@
         <v>12.22</v>
       </c>
       <c r="J622">
-        <v>0.45</v>
+        <v>35.63</v>
       </c>
     </row>
     <row r="623">
@@ -21429,7 +21429,7 @@
         <v>12.1</v>
       </c>
       <c r="J623">
-        <v>0.42</v>
+        <v>33.51</v>
       </c>
     </row>
     <row r="624">
@@ -21467,7 +21467,7 @@
         <v>12.14</v>
       </c>
       <c r="J624">
-        <v>0.49</v>
+        <v>38.82</v>
       </c>
     </row>
     <row r="625">
@@ -21505,7 +21505,7 @@
         <v>12.17</v>
       </c>
       <c r="J625">
-        <v>0.44</v>
+        <v>35.27</v>
       </c>
     </row>
     <row r="626">
@@ -21888,7 +21888,7 @@
         <v>13.7</v>
       </c>
       <c r="J638">
-        <v>0.47</v>
+        <v>37.57</v>
       </c>
     </row>
     <row r="639">
@@ -21923,7 +21923,7 @@
         <v>13.1</v>
       </c>
       <c r="J639">
-        <v>0.59</v>
+        <v>47.28</v>
       </c>
     </row>
     <row r="640">
@@ -21958,7 +21958,7 @@
         <v>13.4</v>
       </c>
       <c r="J640">
-        <v>0.52</v>
+        <v>41.22</v>
       </c>
     </row>
     <row r="641">
@@ -21993,7 +21993,7 @@
         <v>18.9</v>
       </c>
       <c r="J641">
-        <v>0.41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="642">
@@ -22028,7 +22028,7 @@
         <v>18.5</v>
       </c>
       <c r="J642">
-        <v>0.52</v>
+        <v>41.85</v>
       </c>
     </row>
     <row r="643">
@@ -22063,7 +22063,7 @@
         <v>18.7</v>
       </c>
       <c r="J643">
-        <v>0.45</v>
+        <v>36.02</v>
       </c>
     </row>
     <row r="644">
@@ -22098,7 +22098,7 @@
         <v>16.1</v>
       </c>
       <c r="J644">
-        <v>0.37</v>
+        <v>29.93</v>
       </c>
     </row>
     <row r="645">
@@ -22133,7 +22133,7 @@
         <v>16.5</v>
       </c>
       <c r="J645">
-        <v>0.48</v>
+        <v>38.29</v>
       </c>
     </row>
     <row r="646">
@@ -22168,7 +22168,7 @@
         <v>16.3</v>
       </c>
       <c r="J646">
-        <v>0.42</v>
+        <v>33.49</v>
       </c>
     </row>
     <row r="647">
@@ -22203,7 +22203,7 @@
         <v>8.75</v>
       </c>
       <c r="J647">
-        <v>0.34</v>
+        <v>27.49</v>
       </c>
     </row>
     <row r="648">
@@ -22238,7 +22238,7 @@
         <v>8.65</v>
       </c>
       <c r="J648">
-        <v>0.43</v>
+        <v>34.76</v>
       </c>
     </row>
     <row r="649">
@@ -22273,7 +22273,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="J649">
-        <v>0.38</v>
+        <v>30.38</v>
       </c>
     </row>
     <row r="650">
@@ -22308,7 +22308,7 @@
         <v>15.4</v>
       </c>
       <c r="J650">
-        <v>0.33</v>
+        <v>26.69</v>
       </c>
     </row>
     <row r="651">
@@ -22343,7 +22343,7 @@
         <v>14.6</v>
       </c>
       <c r="J651">
-        <v>0.43</v>
+        <v>34.58</v>
       </c>
     </row>
     <row r="652">
@@ -22378,7 +22378,7 @@
         <v>15</v>
       </c>
       <c r="J652">
-        <v>0.37</v>
+        <v>29.85</v>
       </c>
     </row>
     <row r="653">
@@ -22413,7 +22413,7 @@
         <v>15.6</v>
       </c>
       <c r="J653">
-        <v>0.32</v>
+        <v>25.88</v>
       </c>
     </row>
     <row r="654">
@@ -22448,7 +22448,7 @@
         <v>15.4</v>
       </c>
       <c r="J654">
-        <v>0.41</v>
+        <v>33.17</v>
       </c>
     </row>
     <row r="655">
@@ -22483,7 +22483,7 @@
         <v>15.5</v>
       </c>
       <c r="J655">
-        <v>0.36</v>
+        <v>28.48</v>
       </c>
     </row>
     <row r="656">
@@ -22521,7 +22521,7 @@
         <v>19.4</v>
       </c>
       <c r="J656">
-        <v>0.31</v>
+        <v>24.77</v>
       </c>
     </row>
     <row r="657">
@@ -22559,7 +22559,7 @@
         <v>19.6</v>
       </c>
       <c r="J657">
-        <v>0.41</v>
+        <v>32.45</v>
       </c>
     </row>
     <row r="658">
@@ -22597,7 +22597,7 @@
         <v>19.5</v>
       </c>
       <c r="J658">
-        <v>0.35</v>
+        <v>27.85</v>
       </c>
     </row>
     <row r="659">
@@ -22635,7 +22635,7 @@
         <v>15.2</v>
       </c>
       <c r="J659">
-        <v>0.32</v>
+        <v>25.32</v>
       </c>
     </row>
     <row r="660">
@@ -22673,7 +22673,7 @@
         <v>15</v>
       </c>
       <c r="J660">
-        <v>0.41</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="661">
@@ -22711,7 +22711,7 @@
         <v>15.1</v>
       </c>
       <c r="J661">
-        <v>0.35</v>
+        <v>28.11</v>
       </c>
     </row>
     <row r="662">
@@ -22749,7 +22749,7 @@
         <v>12.95</v>
       </c>
       <c r="J662">
-        <v>0.35</v>
+        <v>27.69</v>
       </c>
     </row>
     <row r="663">
@@ -22787,7 +22787,7 @@
         <v>12.65</v>
       </c>
       <c r="J663">
-        <v>0.44</v>
+        <v>35.24</v>
       </c>
     </row>
     <row r="664">
@@ -22825,7 +22825,7 @@
         <v>12.8</v>
       </c>
       <c r="J664">
-        <v>0.38</v>
+        <v>30.17</v>
       </c>
     </row>
     <row r="665">
@@ -22863,7 +22863,7 @@
         <v>14.7</v>
       </c>
       <c r="J665">
-        <v>0.36</v>
+        <v>29.09</v>
       </c>
     </row>
     <row r="666">
@@ -22901,7 +22901,7 @@
         <v>14.5</v>
       </c>
       <c r="J666">
-        <v>0.47</v>
+        <v>37.29</v>
       </c>
     </row>
     <row r="667">
@@ -22939,7 +22939,7 @@
         <v>14.6</v>
       </c>
       <c r="J667">
-        <v>0.4</v>
+        <v>31.88</v>
       </c>
     </row>
     <row r="668">
@@ -22977,7 +22977,7 @@
         <v>7.5</v>
       </c>
       <c r="J668">
-        <v>0.39</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="669">
@@ -23015,7 +23015,7 @@
         <v>7.7</v>
       </c>
       <c r="J669">
-        <v>0.49</v>
+        <v>39.56</v>
       </c>
     </row>
     <row r="670">
@@ -23053,7 +23053,7 @@
         <v>7.6</v>
       </c>
       <c r="J670">
-        <v>0.43</v>
+        <v>34.11</v>
       </c>
     </row>
     <row r="671">
@@ -23091,7 +23091,7 @@
         <v>9.35</v>
       </c>
       <c r="J671">
-        <v>0.42</v>
+        <v>33.46</v>
       </c>
     </row>
     <row r="672">
@@ -23129,7 +23129,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="J672">
-        <v>0.54</v>
+        <v>43.31</v>
       </c>
     </row>
     <row r="673">
@@ -23167,7 +23167,7 @@
         <v>9.4</v>
       </c>
       <c r="J673">
-        <v>0.46</v>
+        <v>36.96</v>
       </c>
     </row>
     <row r="674">
@@ -23205,7 +23205,7 @@
         <v>14.7</v>
       </c>
       <c r="J674">
-        <v>0.44</v>
+        <v>34.85</v>
       </c>
     </row>
     <row r="675">
@@ -23243,7 +23243,7 @@
         <v>14.1</v>
       </c>
       <c r="J675">
-        <v>0.55</v>
+        <v>44.11</v>
       </c>
     </row>
     <row r="676">
@@ -23281,7 +23281,7 @@
         <v>14.4</v>
       </c>
       <c r="J676">
-        <v>0.48</v>
+        <v>38.18</v>
       </c>
     </row>
     <row r="677">
@@ -23339,7 +23339,7 @@
         <v>13.8</v>
       </c>
       <c r="J678">
-        <v>0.42</v>
+        <v>33.42</v>
       </c>
     </row>
     <row r="679">
@@ -23397,7 +23397,7 @@
         <v>13.2</v>
       </c>
       <c r="J680">
-        <v>0.53</v>
+        <v>42.48</v>
       </c>
     </row>
     <row r="681">
@@ -23455,7 +23455,7 @@
         <v>13.5</v>
       </c>
       <c r="J682">
-        <v>0.46</v>
+        <v>36.67</v>
       </c>
     </row>
     <row r="683">
@@ -23513,7 +23513,7 @@
         <v>12.45</v>
       </c>
       <c r="J684">
-        <v>0.44</v>
+        <v>35.54</v>
       </c>
     </row>
     <row r="685">
@@ -23571,7 +23571,7 @@
         <v>11.95</v>
       </c>
       <c r="J686">
-        <v>0.55</v>
+        <v>43.78</v>
       </c>
     </row>
     <row r="687">
@@ -23629,7 +23629,7 @@
         <v>12.2</v>
       </c>
       <c r="J688">
-        <v>0.48</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="689">
@@ -23687,7 +23687,7 @@
         <v>12.85</v>
       </c>
       <c r="J690">
-        <v>0.49</v>
+        <v>39.53</v>
       </c>
     </row>
     <row r="691">
@@ -23745,7 +23745,7 @@
         <v>12.15</v>
       </c>
       <c r="J692">
-        <v>0.6</v>
+        <v>48.07</v>
       </c>
     </row>
     <row r="693">
@@ -23803,7 +23803,7 @@
         <v>12.5</v>
       </c>
       <c r="J694">
-        <v>0.53</v>
+        <v>42.69</v>
       </c>
     </row>
     <row r="695">
@@ -23841,7 +23841,7 @@
         <v>12.49</v>
       </c>
       <c r="J695">
-        <v>0.55</v>
+        <v>43.66</v>
       </c>
     </row>
     <row r="696">
@@ -23879,7 +23879,7 @@
         <v>14.48</v>
       </c>
       <c r="J696">
-        <v>0.66</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="697">
@@ -23917,7 +23917,7 @@
         <v>13.99</v>
       </c>
       <c r="J697">
-        <v>0.59</v>
+        <v>46.93</v>
       </c>
     </row>
     <row r="698">
@@ -23955,7 +23955,7 @@
         <v>12.26</v>
       </c>
       <c r="J698">
-        <v>0.59</v>
+        <v>47.05</v>
       </c>
     </row>
     <row r="699">
@@ -23993,7 +23993,7 @@
         <v>13.5</v>
       </c>
       <c r="J699">
-        <v>0.71</v>
+        <v>56.46</v>
       </c>
     </row>
     <row r="700">
@@ -24031,7 +24031,7 @@
         <v>12.05</v>
       </c>
       <c r="J700">
-        <v>0.63</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="701">
@@ -24069,7 +24069,7 @@
         <v>12.52</v>
       </c>
       <c r="J701">
-        <v>0.6</v>
+        <v>48.21</v>
       </c>
     </row>
     <row r="702">
@@ -24107,7 +24107,7 @@
         <v>12.59</v>
       </c>
       <c r="J702">
-        <v>0.72</v>
+        <v>57.57</v>
       </c>
     </row>
     <row r="703">
@@ -24145,7 +24145,7 @@
         <v>12.74</v>
       </c>
       <c r="J703">
-        <v>0.65</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="704">
@@ -24528,7 +24528,7 @@
         <v>10.9</v>
       </c>
       <c r="J716">
-        <v>0.6</v>
+        <v>47.63</v>
       </c>
     </row>
     <row r="717">
@@ -24563,7 +24563,7 @@
         <v>10.3</v>
       </c>
       <c r="J717">
-        <v>0.77</v>
+        <v>61.49</v>
       </c>
     </row>
     <row r="718">
@@ -24598,7 +24598,7 @@
         <v>10.6</v>
       </c>
       <c r="J718">
-        <v>0.66</v>
+        <v>53.19</v>
       </c>
     </row>
     <row r="719">
@@ -24633,7 +24633,7 @@
         <v>12.5</v>
       </c>
       <c r="J719">
-        <v>0.5600000000000001</v>
+        <v>45.09</v>
       </c>
     </row>
     <row r="720">
@@ -24668,7 +24668,7 @@
         <v>12.1</v>
       </c>
       <c r="J720">
-        <v>0.74</v>
+        <v>59.44</v>
       </c>
     </row>
     <row r="721">
@@ -24703,7 +24703,7 @@
         <v>12.3</v>
       </c>
       <c r="J721">
-        <v>0.64</v>
+        <v>51.22</v>
       </c>
     </row>
     <row r="722">
@@ -24738,7 +24738,7 @@
         <v>12.4</v>
       </c>
       <c r="J722">
-        <v>0.5600000000000001</v>
+        <v>44.67</v>
       </c>
     </row>
     <row r="723">
@@ -24773,7 +24773,7 @@
         <v>12.8</v>
       </c>
       <c r="J723">
-        <v>0.7</v>
+        <v>56.26</v>
       </c>
     </row>
     <row r="724">
@@ -24808,7 +24808,7 @@
         <v>12.6</v>
       </c>
       <c r="J724">
-        <v>0.62</v>
+        <v>49.58</v>
       </c>
     </row>
     <row r="725">
@@ -24843,7 +24843,7 @@
         <v>6.65</v>
       </c>
       <c r="J725">
-        <v>0.5600000000000001</v>
+        <v>44.45</v>
       </c>
     </row>
     <row r="726">
@@ -24878,7 +24878,7 @@
         <v>6.55</v>
       </c>
       <c r="J726">
-        <v>0.72</v>
+        <v>57.24</v>
       </c>
     </row>
     <row r="727">
@@ -24913,7 +24913,7 @@
         <v>6.6</v>
       </c>
       <c r="J727">
-        <v>0.63</v>
+        <v>50.18</v>
       </c>
     </row>
     <row r="728">
@@ -24948,7 +24948,7 @@
         <v>8</v>
       </c>
       <c r="J728">
-        <v>0.52</v>
+        <v>41.85</v>
       </c>
     </row>
     <row r="729">
@@ -24983,7 +24983,7 @@
         <v>7.2</v>
       </c>
       <c r="J729">
-        <v>0.68</v>
+        <v>54.41</v>
       </c>
     </row>
     <row r="730">
@@ -25018,7 +25018,7 @@
         <v>7.6</v>
       </c>
       <c r="J730">
-        <v>0.59</v>
+        <v>47.24</v>
       </c>
     </row>
     <row r="731">
@@ -25053,7 +25053,7 @@
         <v>11.2</v>
       </c>
       <c r="J731">
-        <v>0.5</v>
+        <v>39.64</v>
       </c>
     </row>
     <row r="732">
@@ -25088,7 +25088,7 @@
         <v>11</v>
       </c>
       <c r="J732">
-        <v>0.64</v>
+        <v>51.18</v>
       </c>
     </row>
     <row r="733">
@@ -25123,7 +25123,7 @@
         <v>11.1</v>
       </c>
       <c r="J733">
-        <v>0.5600000000000001</v>
+        <v>44.72</v>
       </c>
     </row>
     <row r="734">
@@ -25161,7 +25161,7 @@
         <v>10.2</v>
       </c>
       <c r="J734">
-        <v>0.49</v>
+        <v>39.49</v>
       </c>
     </row>
     <row r="735">
@@ -25199,7 +25199,7 @@
         <v>10.4</v>
       </c>
       <c r="J735">
-        <v>0.63</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="736">
@@ -25237,7 +25237,7 @@
         <v>10.3</v>
       </c>
       <c r="J736">
-        <v>0.55</v>
+        <v>44.35</v>
       </c>
     </row>
     <row r="737">
@@ -25275,7 +25275,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="J737">
-        <v>0.53</v>
+        <v>42.56</v>
       </c>
     </row>
     <row r="738">
@@ -25313,7 +25313,7 @@
         <v>9.1</v>
       </c>
       <c r="J738">
-        <v>0.65</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="739">
@@ -25351,7 +25351,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="J739">
-        <v>0.59</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="740">
@@ -25389,7 +25389,7 @@
         <v>8.85</v>
       </c>
       <c r="J740">
-        <v>0.57</v>
+        <v>45.68</v>
       </c>
     </row>
     <row r="741">
@@ -25427,7 +25427,7 @@
         <v>8.550000000000001</v>
       </c>
       <c r="J741">
-        <v>0.71</v>
+        <v>56.71</v>
       </c>
     </row>
     <row r="742">
@@ -25465,7 +25465,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="J742">
-        <v>0.63</v>
+        <v>50.44</v>
       </c>
     </row>
     <row r="743">
@@ -25503,7 +25503,7 @@
         <v>7</v>
       </c>
       <c r="J743">
-        <v>0.62</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="744">
@@ -25541,7 +25541,7 @@
         <v>6.8</v>
       </c>
       <c r="J744">
-        <v>0.76</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="745">
@@ -25579,7 +25579,7 @@
         <v>6.9</v>
       </c>
       <c r="J745">
-        <v>0.68</v>
+        <v>54.56</v>
       </c>
     </row>
     <row r="746">
@@ -25617,7 +25617,7 @@
         <v>8.6</v>
       </c>
       <c r="J746">
-        <v>0.6899999999999999</v>
+        <v>55.01</v>
       </c>
     </row>
     <row r="747">
@@ -25655,7 +25655,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="J747">
-        <v>0.86</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="748">
@@ -25693,7 +25693,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="J748">
-        <v>0.76</v>
+        <v>60.65</v>
       </c>
     </row>
     <row r="749">
@@ -25731,7 +25731,7 @@
         <v>7.15</v>
       </c>
       <c r="J749">
-        <v>0.7</v>
+        <v>55.69</v>
       </c>
     </row>
     <row r="750">
@@ -25769,7 +25769,7 @@
         <v>7.25</v>
       </c>
       <c r="J750">
-        <v>0.84</v>
+        <v>67.34999999999999</v>
       </c>
     </row>
     <row r="751">
@@ -25807,7 +25807,7 @@
         <v>7.2</v>
       </c>
       <c r="J751">
-        <v>0.76</v>
+        <v>61.06</v>
       </c>
     </row>
     <row r="752">
@@ -25845,7 +25845,7 @@
         <v>11.8</v>
       </c>
       <c r="J752">
-        <v>0.68</v>
+        <v>54.58</v>
       </c>
     </row>
     <row r="753">
@@ -25883,7 +25883,7 @@
         <v>11.2</v>
       </c>
       <c r="J753">
-        <v>0.82</v>
+        <v>65.73999999999999</v>
       </c>
     </row>
     <row r="754">
@@ -25921,7 +25921,7 @@
         <v>11.5</v>
       </c>
       <c r="J754">
-        <v>0.75</v>
+        <v>59.63</v>
       </c>
     </row>
     <row r="755">
@@ -25979,7 +25979,7 @@
         <v>13.5</v>
       </c>
       <c r="J756">
-        <v>0.61</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="757">
@@ -26037,7 +26037,7 @@
         <v>12.9</v>
       </c>
       <c r="J758">
-        <v>0.74</v>
+        <v>59.58</v>
       </c>
     </row>
     <row r="759">
@@ -26095,7 +26095,7 @@
         <v>13.2</v>
       </c>
       <c r="J760">
-        <v>0.67</v>
+        <v>53.96</v>
       </c>
     </row>
     <row r="761">
@@ -26153,7 +26153,7 @@
         <v>12.15</v>
       </c>
       <c r="J762">
-        <v>0.63</v>
+        <v>50.04</v>
       </c>
     </row>
     <row r="763">
@@ -26211,7 +26211,7 @@
         <v>11.65</v>
       </c>
       <c r="J764">
-        <v>0.74</v>
+        <v>59.24</v>
       </c>
     </row>
     <row r="765">
@@ -26269,7 +26269,7 @@
         <v>11.9</v>
       </c>
       <c r="J766">
-        <v>0.67</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="767">
@@ -26327,7 +26327,7 @@
         <v>14.15</v>
       </c>
       <c r="J768">
-        <v>0.66</v>
+        <v>52.42</v>
       </c>
     </row>
     <row r="769">
@@ -26385,7 +26385,7 @@
         <v>13.45</v>
       </c>
       <c r="J770">
-        <v>0.77</v>
+        <v>61.86</v>
       </c>
     </row>
     <row r="771">
@@ -26443,7 +26443,7 @@
         <v>13.8</v>
       </c>
       <c r="J772">
-        <v>0.71</v>
+        <v>56.97</v>
       </c>
     </row>
     <row r="773">
@@ -26481,7 +26481,7 @@
         <v>12.91</v>
       </c>
       <c r="J773">
-        <v>0.75</v>
+        <v>60.32</v>
       </c>
     </row>
     <row r="774">
@@ -26519,7 +26519,7 @@
         <v>12.82</v>
       </c>
       <c r="J774">
-        <v>0.87</v>
+        <v>69.77</v>
       </c>
     </row>
     <row r="775">
@@ -26557,7 +26557,7 @@
         <v>13</v>
       </c>
       <c r="J775">
-        <v>0.8100000000000001</v>
+        <v>64.76000000000001</v>
       </c>
     </row>
     <row r="776">
@@ -26595,7 +26595,7 @@
         <v>13.52</v>
       </c>
       <c r="J776">
-        <v>0.83</v>
+        <v>66.06</v>
       </c>
     </row>
     <row r="777">
@@ -26633,7 +26633,7 @@
         <v>13.73</v>
       </c>
       <c r="J777">
-        <v>0.95</v>
+        <v>76.38</v>
       </c>
     </row>
     <row r="778">
@@ -26671,7 +26671,7 @@
         <v>13.7</v>
       </c>
       <c r="J778">
-        <v>0.88</v>
+        <v>70.43000000000001</v>
       </c>
     </row>
     <row r="779">
@@ -26709,7 +26709,7 @@
         <v>12.51</v>
       </c>
       <c r="J779">
-        <v>0.86</v>
+        <v>68.81999999999999</v>
       </c>
     </row>
     <row r="780">
@@ -26747,7 +26747,7 @@
         <v>12.81</v>
       </c>
       <c r="J780">
-        <v>0.98</v>
+        <v>78.23999999999999</v>
       </c>
     </row>
     <row r="781">
@@ -26785,7 +26785,7 @@
         <v>12.54</v>
       </c>
       <c r="J781">
-        <v>0.92</v>
+        <v>73.36</v>
       </c>
     </row>
     <row r="782">
@@ -27264,7 +27264,7 @@
         <v>2</v>
       </c>
       <c r="J797">
-        <v>0.38</v>
+        <v>30.68</v>
       </c>
     </row>
     <row r="798">
@@ -27299,7 +27299,7 @@
         <v>1.6</v>
       </c>
       <c r="J798">
-        <v>0.42</v>
+        <v>33.94</v>
       </c>
     </row>
     <row r="799">
@@ -27334,7 +27334,7 @@
         <v>1.8</v>
       </c>
       <c r="J799">
-        <v>0.39</v>
+        <v>31.45</v>
       </c>
     </row>
     <row r="800">
@@ -27369,7 +27369,7 @@
         <v>9</v>
       </c>
       <c r="J800">
-        <v>0.35</v>
+        <v>28.13</v>
       </c>
     </row>
     <row r="801">
@@ -27404,7 +27404,7 @@
         <v>9.4</v>
       </c>
       <c r="J801">
-        <v>0.41</v>
+        <v>33.08</v>
       </c>
     </row>
     <row r="802">
@@ -27439,7 +27439,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="J802">
-        <v>0.37</v>
+        <v>29.41</v>
       </c>
     </row>
     <row r="803">
@@ -27474,7 +27474,7 @@
         <v>5.25</v>
       </c>
       <c r="J803">
-        <v>0.33</v>
+        <v>26.39</v>
       </c>
     </row>
     <row r="804">
@@ -27509,7 +27509,7 @@
         <v>5.15</v>
       </c>
       <c r="J804">
-        <v>0.38</v>
+        <v>30.54</v>
       </c>
     </row>
     <row r="805">
@@ -27544,7 +27544,7 @@
         <v>5.2</v>
       </c>
       <c r="J805">
-        <v>0.35</v>
+        <v>27.65</v>
       </c>
     </row>
     <row r="806">
@@ -27579,7 +27579,7 @@
         <v>7.7</v>
       </c>
       <c r="J806">
-        <v>0.33</v>
+        <v>26.53</v>
       </c>
     </row>
     <row r="807">
@@ -27614,7 +27614,7 @@
         <v>6.9</v>
       </c>
       <c r="J807">
-        <v>0.39</v>
+        <v>31.42</v>
       </c>
     </row>
     <row r="808">
@@ -27649,7 +27649,7 @@
         <v>7.3</v>
       </c>
       <c r="J808">
-        <v>0.35</v>
+        <v>27.86</v>
       </c>
     </row>
     <row r="809">
@@ -27684,7 +27684,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="J809">
-        <v>0.31</v>
+        <v>24.68</v>
       </c>
     </row>
     <row r="810">
@@ -27719,7 +27719,7 @@
         <v>9.1</v>
       </c>
       <c r="J810">
-        <v>0.38</v>
+        <v>30.31</v>
       </c>
     </row>
     <row r="811">
@@ -27754,7 +27754,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="J811">
-        <v>0.33</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="812">
@@ -27792,7 +27792,7 @@
         <v>7.7</v>
       </c>
       <c r="J812">
-        <v>0.3</v>
+        <v>24.14</v>
       </c>
     </row>
     <row r="813">
@@ -27830,7 +27830,7 @@
         <v>7.9</v>
       </c>
       <c r="J813">
-        <v>0.36</v>
+        <v>28.42</v>
       </c>
     </row>
     <row r="814">
@@ -27868,7 +27868,7 @@
         <v>7.8</v>
       </c>
       <c r="J814">
-        <v>0.32</v>
+        <v>25.61</v>
       </c>
     </row>
     <row r="815">
@@ -27906,7 +27906,7 @@
         <v>6.4</v>
       </c>
       <c r="J815">
-        <v>0.28</v>
+        <v>22.69</v>
       </c>
     </row>
     <row r="816">
@@ -27944,7 +27944,7 @@
         <v>6.2</v>
       </c>
       <c r="J816">
-        <v>0.35</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="817">
@@ -27982,7 +27982,7 @@
         <v>6.3</v>
       </c>
       <c r="J817">
-        <v>0.31</v>
+        <v>24.46</v>
       </c>
     </row>
     <row r="818">
@@ -28020,7 +28020,7 @@
         <v>6.25</v>
       </c>
       <c r="J818">
-        <v>0.29</v>
+        <v>23.45</v>
       </c>
     </row>
     <row r="819">
@@ -28058,7 +28058,7 @@
         <v>5.95</v>
       </c>
       <c r="J819">
-        <v>0.36</v>
+        <v>28.65</v>
       </c>
     </row>
     <row r="820">
@@ -28096,7 +28096,7 @@
         <v>6.1</v>
       </c>
       <c r="J820">
-        <v>0.32</v>
+        <v>25.24</v>
       </c>
     </row>
     <row r="821">
@@ -28134,7 +28134,7 @@
         <v>11.4</v>
       </c>
       <c r="J821">
-        <v>0.3</v>
+        <v>24.25</v>
       </c>
     </row>
     <row r="822">
@@ -28172,7 +28172,7 @@
         <v>11.2</v>
       </c>
       <c r="J822">
-        <v>0.37</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="823">
@@ -28210,7 +28210,7 @@
         <v>11.3</v>
       </c>
       <c r="J823">
-        <v>0.32</v>
+        <v>25.95</v>
       </c>
     </row>
     <row r="824">
@@ -28248,7 +28248,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="J824">
-        <v>0.31</v>
+        <v>24.59</v>
       </c>
     </row>
     <row r="825">
@@ -28286,7 +28286,7 @@
         <v>10</v>
       </c>
       <c r="J825">
-        <v>0.38</v>
+        <v>30.23</v>
       </c>
     </row>
     <row r="826">
@@ -28324,7 +28324,7 @@
         <v>9.9</v>
       </c>
       <c r="J826">
-        <v>0.33</v>
+        <v>26.48</v>
       </c>
     </row>
     <row r="827">
@@ -28362,7 +28362,7 @@
         <v>10.05</v>
       </c>
       <c r="J827">
-        <v>0.33</v>
+        <v>26.24</v>
       </c>
     </row>
     <row r="828">
@@ -28400,7 +28400,7 @@
         <v>10.15</v>
       </c>
       <c r="J828">
-        <v>0.41</v>
+        <v>32.69</v>
       </c>
     </row>
     <row r="829">
@@ -28438,7 +28438,7 @@
         <v>10.1</v>
       </c>
       <c r="J829">
-        <v>0.35</v>
+        <v>28.17</v>
       </c>
     </row>
     <row r="830">
@@ -28476,7 +28476,7 @@
         <v>14</v>
       </c>
       <c r="J830">
-        <v>0.33</v>
+        <v>26.77</v>
       </c>
     </row>
     <row r="831">
@@ -28514,7 +28514,7 @@
         <v>13.4</v>
       </c>
       <c r="J831">
-        <v>0.4</v>
+        <v>31.92</v>
       </c>
     </row>
     <row r="832">
@@ -28552,7 +28552,7 @@
         <v>13.7</v>
       </c>
       <c r="J832">
-        <v>0.35</v>
+        <v>28.21</v>
       </c>
     </row>
     <row r="833">
@@ -28610,7 +28610,7 @@
         <v>12.1</v>
       </c>
       <c r="J834">
-        <v>0.34</v>
+        <v>27.44</v>
       </c>
     </row>
     <row r="835">
@@ -28668,7 +28668,7 @@
         <v>11.5</v>
       </c>
       <c r="J836">
-        <v>0.4</v>
+        <v>32.32</v>
       </c>
     </row>
     <row r="837">
@@ -28726,7 +28726,7 @@
         <v>11.8</v>
       </c>
       <c r="J838">
-        <v>0.36</v>
+        <v>28.51</v>
       </c>
     </row>
     <row r="839">
@@ -28784,7 +28784,7 @@
         <v>12.65</v>
       </c>
       <c r="J840">
-        <v>0.35</v>
+        <v>27.89</v>
       </c>
     </row>
     <row r="841">
@@ -28842,7 +28842,7 @@
         <v>12.15</v>
       </c>
       <c r="J842">
-        <v>0.39</v>
+        <v>31.23</v>
       </c>
     </row>
     <row r="843">
@@ -28900,7 +28900,7 @@
         <v>12.4</v>
       </c>
       <c r="J844">
-        <v>0.36</v>
+        <v>28.76</v>
       </c>
     </row>
     <row r="845">
@@ -28958,7 +28958,7 @@
         <v>13.75</v>
       </c>
       <c r="J846">
-        <v>0.35</v>
+        <v>27.97</v>
       </c>
     </row>
     <row r="847">
@@ -29016,7 +29016,7 @@
         <v>13.05</v>
       </c>
       <c r="J848">
-        <v>0.4</v>
+        <v>31.92</v>
       </c>
     </row>
     <row r="849">
@@ -29074,7 +29074,7 @@
         <v>13.4</v>
       </c>
       <c r="J850">
-        <v>0.37</v>
+        <v>29.21</v>
       </c>
     </row>
     <row r="851">
@@ -29112,7 +29112,7 @@
         <v>12.27</v>
       </c>
       <c r="J851">
-        <v>0.38</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="852">
@@ -29150,7 +29150,7 @@
         <v>12.66</v>
       </c>
       <c r="J852">
-        <v>0.43</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="853">
@@ -29188,7 +29188,7 @@
         <v>12.33</v>
       </c>
       <c r="J853">
-        <v>0.39</v>
+        <v>31.43</v>
       </c>
     </row>
     <row r="854">
@@ -29226,7 +29226,7 @@
         <v>12.95</v>
       </c>
       <c r="J854">
-        <v>0.38</v>
+        <v>30.78</v>
       </c>
     </row>
     <row r="855">
@@ -29264,7 +29264,7 @@
         <v>12.76</v>
       </c>
       <c r="J855">
-        <v>0.43</v>
+        <v>34.75</v>
       </c>
     </row>
     <row r="856">
@@ -29302,7 +29302,7 @@
         <v>13.01</v>
       </c>
       <c r="J856">
-        <v>0.39</v>
+        <v>31.58</v>
       </c>
     </row>
     <row r="857">
@@ -29340,7 +29340,7 @@
         <v>12.36</v>
       </c>
       <c r="J857">
-        <v>0.39</v>
+        <v>31.49</v>
       </c>
     </row>
     <row r="858">
@@ -29378,7 +29378,7 @@
         <v>12.52</v>
       </c>
       <c r="J858">
-        <v>0.44</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="859">
@@ -29416,7 +29416,7 @@
         <v>12.42</v>
       </c>
       <c r="J859">
-        <v>0.4</v>
+        <v>32.09</v>
       </c>
     </row>
     <row r="860">
@@ -29799,7 +29799,7 @@
         <v>3.7</v>
       </c>
       <c r="J872">
-        <v>0.58</v>
+        <v>46.68</v>
       </c>
     </row>
     <row r="873">
@@ -29834,7 +29834,7 @@
         <v>3.1</v>
       </c>
       <c r="J873">
-        <v>0.73</v>
+        <v>58.11</v>
       </c>
     </row>
     <row r="874">
@@ -29869,7 +29869,7 @@
         <v>3.4</v>
       </c>
       <c r="J874">
-        <v>0.62</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="875">
@@ -29904,7 +29904,7 @@
         <v>6.9</v>
       </c>
       <c r="J875">
-        <v>0.51</v>
+        <v>41.06</v>
       </c>
     </row>
     <row r="876">
@@ -29939,7 +29939,7 @@
         <v>6.5</v>
       </c>
       <c r="J876">
-        <v>0.62</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="877">
@@ -29974,7 +29974,7 @@
         <v>6.7</v>
       </c>
       <c r="J877">
-        <v>0.55</v>
+        <v>43.92</v>
       </c>
     </row>
     <row r="878">
@@ -30009,7 +30009,7 @@
         <v>6.8</v>
       </c>
       <c r="J878">
-        <v>0.44</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="879">
@@ -30044,7 +30044,7 @@
         <v>7.2</v>
       </c>
       <c r="J879">
-        <v>0.54</v>
+        <v>43.54</v>
       </c>
     </row>
     <row r="880">
@@ -30079,7 +30079,7 @@
         <v>7</v>
       </c>
       <c r="J880">
-        <v>0.47</v>
+        <v>37.92</v>
       </c>
     </row>
     <row r="881">
@@ -30114,7 +30114,7 @@
         <v>5.65</v>
       </c>
       <c r="J881">
-        <v>0.42</v>
+        <v>33.45</v>
       </c>
     </row>
     <row r="882">
@@ -30149,7 +30149,7 @@
         <v>5.55</v>
       </c>
       <c r="J882">
-        <v>0.51</v>
+        <v>41.18</v>
       </c>
     </row>
     <row r="883">
@@ -30184,7 +30184,7 @@
         <v>5.6</v>
       </c>
       <c r="J883">
-        <v>0.45</v>
+        <v>36.18</v>
       </c>
     </row>
     <row r="884">
@@ -30219,7 +30219,7 @@
         <v>8</v>
       </c>
       <c r="J884">
-        <v>0.41</v>
+        <v>32.44</v>
       </c>
     </row>
     <row r="885">
@@ -30254,7 +30254,7 @@
         <v>7.2</v>
       </c>
       <c r="J885">
-        <v>0.51</v>
+        <v>40.49</v>
       </c>
     </row>
     <row r="886">
@@ -30289,7 +30289,7 @@
         <v>7.6</v>
       </c>
       <c r="J886">
-        <v>0.45</v>
+        <v>35.61</v>
       </c>
     </row>
     <row r="887">
@@ -30324,7 +30324,7 @@
         <v>6</v>
       </c>
       <c r="J887">
-        <v>0.36</v>
+        <v>28.48</v>
       </c>
     </row>
     <row r="888">
@@ -30359,7 +30359,7 @@
         <v>5.8</v>
       </c>
       <c r="J888">
-        <v>0.45</v>
+        <v>36.21</v>
       </c>
     </row>
     <row r="889">
@@ -30394,7 +30394,7 @@
         <v>5.9</v>
       </c>
       <c r="J889">
-        <v>0.4</v>
+        <v>31.61</v>
       </c>
     </row>
     <row r="890">
@@ -30432,7 +30432,7 @@
         <v>7.3</v>
       </c>
       <c r="J890">
-        <v>0.35</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="891">
@@ -30470,7 +30470,7 @@
         <v>7.5</v>
       </c>
       <c r="J891">
-        <v>0.44</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="892">
@@ -30508,7 +30508,7 @@
         <v>7.4</v>
       </c>
       <c r="J892">
-        <v>0.39</v>
+        <v>30.82</v>
       </c>
     </row>
     <row r="893">
@@ -30546,7 +30546,7 @@
         <v>7.9</v>
       </c>
       <c r="J893">
-        <v>0.34</v>
+        <v>26.83</v>
       </c>
     </row>
     <row r="894">
@@ -30584,7 +30584,7 @@
         <v>7.7</v>
       </c>
       <c r="J894">
-        <v>0.43</v>
+        <v>34.16</v>
       </c>
     </row>
     <row r="895">
@@ -30622,7 +30622,7 @@
         <v>7.8</v>
       </c>
       <c r="J895">
-        <v>0.37</v>
+        <v>29.95</v>
       </c>
     </row>
     <row r="896">
@@ -30660,7 +30660,7 @@
         <v>6.55</v>
       </c>
       <c r="J896">
-        <v>0.33</v>
+        <v>26.04</v>
       </c>
     </row>
     <row r="897">
@@ -30698,7 +30698,7 @@
         <v>6.25</v>
       </c>
       <c r="J897">
-        <v>0.42</v>
+        <v>33.85</v>
       </c>
     </row>
     <row r="898">
@@ -30736,7 +30736,7 @@
         <v>6.4</v>
       </c>
       <c r="J898">
-        <v>0.36</v>
+        <v>28.99</v>
       </c>
     </row>
     <row r="899">
@@ -30774,7 +30774,7 @@
         <v>4.6</v>
       </c>
       <c r="J899">
-        <v>0.33</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="900">
@@ -30812,7 +30812,7 @@
         <v>4.4</v>
       </c>
       <c r="J900">
-        <v>0.42</v>
+        <v>33.84</v>
       </c>
     </row>
     <row r="901">
@@ -30850,7 +30850,7 @@
         <v>4.5</v>
       </c>
       <c r="J901">
-        <v>0.36</v>
+        <v>29.17</v>
       </c>
     </row>
     <row r="902">
@@ -30888,7 +30888,7 @@
         <v>3.8</v>
       </c>
       <c r="J902">
-        <v>0.35</v>
+        <v>28.11</v>
       </c>
     </row>
     <row r="903">
@@ -30926,7 +30926,7 @@
         <v>4</v>
       </c>
       <c r="J903">
-        <v>0.44</v>
+        <v>35.44</v>
       </c>
     </row>
     <row r="904">
@@ -30964,7 +30964,7 @@
         <v>3.9</v>
       </c>
       <c r="J904">
-        <v>0.38</v>
+        <v>30.76</v>
       </c>
     </row>
     <row r="905">
@@ -31002,7 +31002,7 @@
         <v>5.55</v>
       </c>
       <c r="J905">
-        <v>0.37</v>
+        <v>29.52</v>
       </c>
     </row>
     <row r="906">
@@ -31040,7 +31040,7 @@
         <v>5.65</v>
       </c>
       <c r="J906">
-        <v>0.47</v>
+        <v>37.49</v>
       </c>
     </row>
     <row r="907">
@@ -31078,7 +31078,7 @@
         <v>5.6</v>
       </c>
       <c r="J907">
-        <v>0.41</v>
+        <v>32.71</v>
       </c>
     </row>
     <row r="908">
@@ -31116,7 +31116,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="J908">
-        <v>0.39</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="909">
@@ -31154,7 +31154,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J909">
-        <v>0.49</v>
+        <v>39.22</v>
       </c>
     </row>
     <row r="910">
@@ -31192,7 +31192,7 @@
         <v>8.5</v>
       </c>
       <c r="J910">
-        <v>0.42</v>
+        <v>33.92</v>
       </c>
     </row>
     <row r="911">
@@ -31250,7 +31250,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="J912">
-        <v>0.4</v>
+        <v>31.99</v>
       </c>
     </row>
     <row r="913">
@@ -31308,7 +31308,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="J914">
-        <v>0.5</v>
+        <v>40.18</v>
       </c>
     </row>
     <row r="915">
@@ -31366,7 +31366,7 @@
         <v>9</v>
       </c>
       <c r="J916">
-        <v>0.43</v>
+        <v>34.38</v>
       </c>
     </row>
     <row r="917">
@@ -31424,7 +31424,7 @@
         <v>9.65</v>
       </c>
       <c r="J918">
-        <v>0.39</v>
+        <v>30.85</v>
       </c>
     </row>
     <row r="919">
@@ -31482,7 +31482,7 @@
         <v>9.15</v>
       </c>
       <c r="J920">
-        <v>0.49</v>
+        <v>39.05</v>
       </c>
     </row>
     <row r="921">
@@ -31540,7 +31540,7 @@
         <v>9.4</v>
       </c>
       <c r="J922">
-        <v>0.43</v>
+        <v>34.61</v>
       </c>
     </row>
     <row r="923">
@@ -31598,7 +31598,7 @@
         <v>9.550000000000001</v>
       </c>
       <c r="J924">
-        <v>0.4</v>
+        <v>32.25</v>
       </c>
     </row>
     <row r="925">
@@ -31656,7 +31656,7 @@
         <v>8.85</v>
       </c>
       <c r="J926">
-        <v>0.5</v>
+        <v>39.71</v>
       </c>
     </row>
     <row r="927">
@@ -31714,7 +31714,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="J928">
-        <v>0.44</v>
+        <v>34.92</v>
       </c>
     </row>
     <row r="929">
@@ -31752,7 +31752,7 @@
         <v>10.05</v>
       </c>
       <c r="J929">
-        <v>0.43</v>
+        <v>34.14</v>
       </c>
     </row>
     <row r="930">
@@ -31790,7 +31790,7 @@
         <v>9.380000000000001</v>
       </c>
       <c r="J930">
-        <v>0.53</v>
+        <v>42.01</v>
       </c>
     </row>
     <row r="931">
@@ -31828,7 +31828,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="J931">
-        <v>0.47</v>
+        <v>37.48</v>
       </c>
     </row>
     <row r="932">
@@ -31866,7 +31866,7 @@
         <v>11.45</v>
       </c>
       <c r="J932">
-        <v>0.44</v>
+        <v>35.44</v>
       </c>
     </row>
     <row r="933">
@@ -31904,7 +31904,7 @@
         <v>9.48</v>
       </c>
       <c r="J933">
-        <v>0.54</v>
+        <v>43.33</v>
       </c>
     </row>
     <row r="934">
@@ -31942,7 +31942,7 @@
         <v>9.630000000000001</v>
       </c>
       <c r="J934">
-        <v>0.48</v>
+        <v>38.79</v>
       </c>
     </row>
     <row r="935">
@@ -31980,7 +31980,7 @@
         <v>12.2</v>
       </c>
       <c r="J935">
-        <v>0.44</v>
+        <v>35.42</v>
       </c>
     </row>
     <row r="936">
@@ -32018,7 +32018,7 @@
         <v>9.619999999999999</v>
       </c>
       <c r="J936">
-        <v>0.54</v>
+        <v>42.85</v>
       </c>
     </row>
     <row r="937">
@@ -32056,7 +32056,7 @@
         <v>10.11</v>
       </c>
       <c r="J937">
-        <v>0.48</v>
+        <v>38.66</v>
       </c>
     </row>
     <row r="938">
@@ -32439,7 +32439,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="J950">
-        <v>0.83</v>
+        <v>66.15000000000001</v>
       </c>
     </row>
     <row r="951">
@@ -32474,7 +32474,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J951">
-        <v>0.98</v>
+        <v>78.25</v>
       </c>
     </row>
     <row r="952">
@@ -32509,7 +32509,7 @@
         <v>8.5</v>
       </c>
       <c r="J952">
-        <v>0.9</v>
+        <v>71.59999999999999</v>
       </c>
     </row>
     <row r="953">
@@ -32544,7 +32544,7 @@
         <v>18.8</v>
       </c>
       <c r="J953">
-        <v>0.68</v>
+        <v>54.28</v>
       </c>
     </row>
     <row r="954">
@@ -32579,7 +32579,7 @@
         <v>18.4</v>
       </c>
       <c r="J954">
-        <v>0.8100000000000001</v>
+        <v>64.45999999999999</v>
       </c>
     </row>
     <row r="955">
@@ -32614,7 +32614,7 @@
         <v>18.6</v>
       </c>
       <c r="J955">
-        <v>0.74</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="956">
@@ -32649,7 +32649,7 @@
         <v>13.5</v>
       </c>
       <c r="J956">
-        <v>0.6</v>
+        <v>47.73</v>
       </c>
     </row>
     <row r="957">
@@ -32684,7 +32684,7 @@
         <v>13.9</v>
       </c>
       <c r="J957">
-        <v>0.68</v>
+        <v>54.29</v>
       </c>
     </row>
     <row r="958">
@@ -32719,7 +32719,7 @@
         <v>13.7</v>
       </c>
       <c r="J958">
-        <v>0.64</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="959">
@@ -32754,7 +32754,7 @@
         <v>17.45</v>
       </c>
       <c r="J959">
-        <v>0.53</v>
+        <v>42.12</v>
       </c>
     </row>
     <row r="960">
@@ -32789,7 +32789,7 @@
         <v>17.35</v>
       </c>
       <c r="J960">
-        <v>0.6</v>
+        <v>48.34</v>
       </c>
     </row>
     <row r="961">
@@ -32824,7 +32824,7 @@
         <v>17.4</v>
       </c>
       <c r="J961">
-        <v>0.57</v>
+        <v>45.59</v>
       </c>
     </row>
     <row r="962">
@@ -32859,7 +32859,7 @@
         <v>18.1</v>
       </c>
       <c r="J962">
-        <v>0.5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="963">
@@ -32894,7 +32894,7 @@
         <v>17.3</v>
       </c>
       <c r="J963">
-        <v>0.57</v>
+        <v>45.91</v>
       </c>
     </row>
     <row r="964">
@@ -32929,7 +32929,7 @@
         <v>17.7</v>
       </c>
       <c r="J964">
-        <v>0.54</v>
+        <v>43.15</v>
       </c>
     </row>
     <row r="965">
@@ -32964,7 +32964,7 @@
         <v>19.5</v>
       </c>
       <c r="J965">
-        <v>0.47</v>
+        <v>37.81</v>
       </c>
     </row>
     <row r="966">
@@ -32999,7 +32999,7 @@
         <v>19.3</v>
       </c>
       <c r="J966">
-        <v>0.54</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="967">
@@ -33034,7 +33034,7 @@
         <v>19.4</v>
       </c>
       <c r="J967">
-        <v>0.51</v>
+        <v>40.46</v>
       </c>
     </row>
     <row r="968">
@@ -33072,7 +33072,7 @@
         <v>21.2</v>
       </c>
       <c r="J968">
-        <v>0.46</v>
+        <v>36.55</v>
       </c>
     </row>
     <row r="969">
@@ -33110,7 +33110,7 @@
         <v>21.4</v>
       </c>
       <c r="J969">
-        <v>0.54</v>
+        <v>43.37</v>
       </c>
     </row>
     <row r="970">
@@ -33148,7 +33148,7 @@
         <v>21.3</v>
       </c>
       <c r="J970">
-        <v>0.5</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="971">
@@ -33186,7 +33186,7 @@
         <v>21.8</v>
       </c>
       <c r="J971">
-        <v>0.5</v>
+        <v>40.38</v>
       </c>
     </row>
     <row r="972">
@@ -33224,7 +33224,7 @@
         <v>21.6</v>
       </c>
       <c r="J972">
-        <v>0.58</v>
+        <v>46.48</v>
       </c>
     </row>
     <row r="973">
@@ -33262,7 +33262,7 @@
         <v>21.7</v>
       </c>
       <c r="J973">
-        <v>0.54</v>
+        <v>43.38</v>
       </c>
     </row>
     <row r="974">
@@ -33300,7 +33300,7 @@
         <v>12.75</v>
       </c>
       <c r="J974">
-        <v>0.59</v>
+        <v>47.55</v>
       </c>
     </row>
     <row r="975">
@@ -33338,7 +33338,7 @@
         <v>12.45</v>
       </c>
       <c r="J975">
-        <v>0.68</v>
+        <v>54.38</v>
       </c>
     </row>
     <row r="976">
@@ -33376,7 +33376,7 @@
         <v>12.6</v>
       </c>
       <c r="J976">
-        <v>0.63</v>
+        <v>50.73</v>
       </c>
     </row>
     <row r="977">
@@ -33414,7 +33414,7 @@
         <v>15.5</v>
       </c>
       <c r="J977">
-        <v>0.71</v>
+        <v>56.83</v>
       </c>
     </row>
     <row r="978">
@@ -33452,7 +33452,7 @@
         <v>15.3</v>
       </c>
       <c r="J978">
-        <v>0.79</v>
+        <v>63.55</v>
       </c>
     </row>
     <row r="979">
@@ -33490,7 +33490,7 @@
         <v>15.4</v>
       </c>
       <c r="J979">
-        <v>0.75</v>
+        <v>59.75</v>
       </c>
     </row>
     <row r="980">
@@ -33528,7 +33528,7 @@
         <v>10.1</v>
       </c>
       <c r="J980">
-        <v>0.7</v>
+        <v>56.08</v>
       </c>
     </row>
     <row r="981">
@@ -33566,7 +33566,7 @@
         <v>10.3</v>
       </c>
       <c r="J981">
-        <v>0.8</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="982">
@@ -33604,7 +33604,7 @@
         <v>10.2</v>
       </c>
       <c r="J982">
-        <v>0.74</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="983">
@@ -33642,7 +33642,7 @@
         <v>13.95</v>
       </c>
       <c r="J983">
-        <v>0.7</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="984">
@@ -33680,7 +33680,7 @@
         <v>14.05</v>
       </c>
       <c r="J984">
-        <v>0.77</v>
+        <v>61.81</v>
       </c>
     </row>
     <row r="985">
@@ -33718,7 +33718,7 @@
         <v>14</v>
       </c>
       <c r="J985">
-        <v>0.74</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="986">
@@ -33756,7 +33756,7 @@
         <v>13.4</v>
       </c>
       <c r="J986">
-        <v>0.68</v>
+        <v>54.38</v>
       </c>
     </row>
     <row r="987">
@@ -33794,7 +33794,7 @@
         <v>12.8</v>
       </c>
       <c r="J987">
-        <v>0.79</v>
+        <v>63.28</v>
       </c>
     </row>
     <row r="988">
@@ -33832,7 +33832,7 @@
         <v>13.1</v>
       </c>
       <c r="J988">
-        <v>0.73</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="989">
@@ -33890,7 +33890,7 @@
         <v>20.6</v>
       </c>
       <c r="J990">
-        <v>0.63</v>
+        <v>50.35</v>
       </c>
     </row>
     <row r="991">
@@ -33948,7 +33948,7 @@
         <v>20</v>
       </c>
       <c r="J992">
-        <v>0.7</v>
+        <v>55.94</v>
       </c>
     </row>
     <row r="993">
@@ -34006,7 +34006,7 @@
         <v>20.3</v>
       </c>
       <c r="J994">
-        <v>0.66</v>
+        <v>53.03</v>
       </c>
     </row>
     <row r="995">
@@ -34064,7 +34064,7 @@
         <v>20.75</v>
       </c>
       <c r="J996">
-        <v>0.66</v>
+        <v>52.82</v>
       </c>
     </row>
     <row r="997">
@@ -34122,7 +34122,7 @@
         <v>20.25</v>
       </c>
       <c r="J998">
-        <v>0.6899999999999999</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="999">
@@ -34180,7 +34180,7 @@
         <v>20.5</v>
       </c>
       <c r="J1000">
-        <v>0.67</v>
+        <v>53.45</v>
       </c>
     </row>
     <row r="1001">
@@ -34238,7 +34238,7 @@
         <v>16.15</v>
       </c>
       <c r="J1002">
-        <v>0.78</v>
+        <v>62.15</v>
       </c>
     </row>
     <row r="1003">
@@ -34296,7 +34296,7 @@
         <v>15.45</v>
       </c>
       <c r="J1004">
-        <v>0.82</v>
+        <v>65.34</v>
       </c>
     </row>
     <row r="1005">
@@ -34354,7 +34354,7 @@
         <v>15.8</v>
       </c>
       <c r="J1006">
-        <v>0.8</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="1007">
@@ -34392,7 +34392,7 @@
         <v>16</v>
       </c>
       <c r="J1007">
-        <v>0.86</v>
+        <v>69.12</v>
       </c>
     </row>
     <row r="1008">
@@ -34430,7 +34430,7 @@
         <v>16.02</v>
       </c>
       <c r="J1008">
-        <v>0.9</v>
+        <v>72.33</v>
       </c>
     </row>
     <row r="1009">
@@ -34468,7 +34468,7 @@
         <v>15.96</v>
       </c>
       <c r="J1009">
-        <v>0.87</v>
+        <v>69.97</v>
       </c>
     </row>
     <row r="1010">
@@ -34506,7 +34506,7 @@
         <v>15.73</v>
       </c>
       <c r="J1010">
-        <v>0.89</v>
+        <v>71.18000000000001</v>
       </c>
     </row>
     <row r="1011">
@@ -34544,7 +34544,7 @@
         <v>15.7</v>
       </c>
       <c r="J1011">
-        <v>0.9399999999999999</v>
+        <v>75.52</v>
       </c>
     </row>
     <row r="1012">
@@ -34582,7 +34582,7 @@
         <v>15.69</v>
       </c>
       <c r="J1012">
-        <v>0.91</v>
+        <v>72.94</v>
       </c>
     </row>
     <row r="1013">
@@ -34620,7 +34620,7 @@
         <v>15.83</v>
       </c>
       <c r="J1013">
-        <v>0.9</v>
+        <v>71.95999999999999</v>
       </c>
     </row>
     <row r="1014">
@@ -34658,7 +34658,7 @@
         <v>15.69</v>
       </c>
       <c r="J1014">
-        <v>0.95</v>
+        <v>76.25</v>
       </c>
     </row>
     <row r="1015">
@@ -34696,7 +34696,7 @@
         <v>15.65</v>
       </c>
       <c r="J1015">
-        <v>0.91</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="1016">
@@ -35271,7 +35271,7 @@
         <v>12.1</v>
       </c>
       <c r="J1034">
-        <v>0.38</v>
+        <v>30.15</v>
       </c>
     </row>
     <row r="1035">
@@ -35306,7 +35306,7 @@
         <v>12.5</v>
       </c>
       <c r="J1035">
-        <v>0.49</v>
+        <v>39.31</v>
       </c>
     </row>
     <row r="1036">
@@ -35341,7 +35341,7 @@
         <v>12.3</v>
       </c>
       <c r="J1036">
-        <v>0.41</v>
+        <v>33.03</v>
       </c>
     </row>
     <row r="1037">
@@ -35376,7 +35376,7 @@
         <v>10.75</v>
       </c>
       <c r="J1037">
-        <v>0.35</v>
+        <v>27.87</v>
       </c>
     </row>
     <row r="1038">
@@ -35411,7 +35411,7 @@
         <v>10.65</v>
       </c>
       <c r="J1038">
-        <v>0.47</v>
+        <v>37.55</v>
       </c>
     </row>
     <row r="1039">
@@ -35446,7 +35446,7 @@
         <v>10.7</v>
       </c>
       <c r="J1039">
-        <v>0.39</v>
+        <v>30.84</v>
       </c>
     </row>
     <row r="1040">
@@ -35481,7 +35481,7 @@
         <v>11.2</v>
       </c>
       <c r="J1040">
-        <v>0.35</v>
+        <v>28.33</v>
       </c>
     </row>
     <row r="1041">
@@ -35516,7 +35516,7 @@
         <v>10.4</v>
       </c>
       <c r="J1041">
-        <v>0.48</v>
+        <v>38.03</v>
       </c>
     </row>
     <row r="1042">
@@ -35551,7 +35551,7 @@
         <v>10.8</v>
       </c>
       <c r="J1042">
-        <v>0.4</v>
+        <v>32.02</v>
       </c>
     </row>
     <row r="1043">
@@ -35586,7 +35586,7 @@
         <v>11.1</v>
       </c>
       <c r="J1043">
-        <v>0.33</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="1044">
@@ -35621,7 +35621,7 @@
         <v>10.9</v>
       </c>
       <c r="J1044">
-        <v>0.43</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1045">
@@ -35656,7 +35656,7 @@
         <v>11</v>
       </c>
       <c r="J1045">
-        <v>0.37</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="1046">
@@ -35694,7 +35694,7 @@
         <v>11.3</v>
       </c>
       <c r="J1046">
-        <v>0.29</v>
+        <v>23.06</v>
       </c>
     </row>
     <row r="1047">
@@ -35732,7 +35732,7 @@
         <v>11.5</v>
       </c>
       <c r="J1047">
-        <v>0.38</v>
+        <v>30.34</v>
       </c>
     </row>
     <row r="1048">
@@ -35770,7 +35770,7 @@
         <v>11.4</v>
       </c>
       <c r="J1048">
-        <v>0.32</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="1049">
@@ -35808,7 +35808,7 @@
         <v>16.3</v>
       </c>
       <c r="J1049">
-        <v>0.29</v>
+        <v>22.94</v>
       </c>
     </row>
     <row r="1050">
@@ -35846,7 +35846,7 @@
         <v>16.1</v>
       </c>
       <c r="J1050">
-        <v>0.37</v>
+        <v>29.96</v>
       </c>
     </row>
     <row r="1051">
@@ -35884,7 +35884,7 @@
         <v>16.2</v>
       </c>
       <c r="J1051">
-        <v>0.32</v>
+        <v>25.59</v>
       </c>
     </row>
     <row r="1052">
@@ -35922,7 +35922,7 @@
         <v>12.65</v>
       </c>
       <c r="J1052">
-        <v>0.29</v>
+        <v>23.26</v>
       </c>
     </row>
     <row r="1053">
@@ -35960,7 +35960,7 @@
         <v>12.35</v>
       </c>
       <c r="J1053">
-        <v>0.37</v>
+        <v>29.81</v>
       </c>
     </row>
     <row r="1054">
@@ -35998,7 +35998,7 @@
         <v>12.5</v>
       </c>
       <c r="J1054">
-        <v>0.32</v>
+        <v>25.44</v>
       </c>
     </row>
     <row r="1055">
@@ -36036,7 +36036,7 @@
         <v>4.5</v>
       </c>
       <c r="J1055">
-        <v>0.3</v>
+        <v>24.16</v>
       </c>
     </row>
     <row r="1056">
@@ -36074,7 +36074,7 @@
         <v>4.3</v>
       </c>
       <c r="J1056">
-        <v>0.4</v>
+        <v>31.74</v>
       </c>
     </row>
     <row r="1057">
@@ -36112,7 +36112,7 @@
         <v>4.4</v>
       </c>
       <c r="J1057">
-        <v>0.33</v>
+        <v>26.63</v>
       </c>
     </row>
     <row r="1058">
@@ -36150,7 +36150,7 @@
         <v>7.8</v>
       </c>
       <c r="J1058">
-        <v>0.32</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="1059">
@@ -36188,7 +36188,7 @@
         <v>8</v>
       </c>
       <c r="J1059">
-        <v>0.42</v>
+        <v>33.78</v>
       </c>
     </row>
     <row r="1060">
@@ -36226,7 +36226,7 @@
         <v>7.9</v>
       </c>
       <c r="J1060">
-        <v>0.35</v>
+        <v>28.37</v>
       </c>
     </row>
     <row r="1061">
@@ -36264,7 +36264,7 @@
         <v>4.85</v>
       </c>
       <c r="J1061">
-        <v>0.34</v>
+        <v>27.19</v>
       </c>
     </row>
     <row r="1062">
@@ -36302,7 +36302,7 @@
         <v>4.95</v>
       </c>
       <c r="J1062">
-        <v>0.44</v>
+        <v>35.41</v>
       </c>
     </row>
     <row r="1063">
@@ -36340,7 +36340,7 @@
         <v>4.9</v>
       </c>
       <c r="J1063">
-        <v>0.37</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="1064">
@@ -36378,7 +36378,7 @@
         <v>8.5</v>
       </c>
       <c r="J1064">
-        <v>0.36</v>
+        <v>28.53</v>
       </c>
     </row>
     <row r="1065">
@@ -36416,7 +36416,7 @@
         <v>7.9</v>
       </c>
       <c r="J1065">
-        <v>0.46</v>
+        <v>37.14</v>
       </c>
     </row>
     <row r="1066">
@@ -36454,7 +36454,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J1066">
-        <v>0.39</v>
+        <v>31.01</v>
       </c>
     </row>
     <row r="1067">
@@ -36512,7 +36512,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="J1068">
-        <v>0.36</v>
+        <v>28.46</v>
       </c>
     </row>
     <row r="1069">
@@ -36570,7 +36570,7 @@
         <v>7.7</v>
       </c>
       <c r="J1070">
-        <v>0.46</v>
+        <v>36.62</v>
       </c>
     </row>
     <row r="1071">
@@ -36628,7 +36628,7 @@
         <v>8</v>
       </c>
       <c r="J1072">
-        <v>0.39</v>
+        <v>31.42</v>
       </c>
     </row>
     <row r="1073">
@@ -36686,7 +36686,7 @@
         <v>8.050000000000001</v>
       </c>
       <c r="J1074">
-        <v>0.35</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="1075">
@@ -36744,7 +36744,7 @@
         <v>7.55</v>
       </c>
       <c r="J1076">
-        <v>0.46</v>
+        <v>37.08</v>
       </c>
     </row>
     <row r="1077">
@@ -36802,7 +36802,7 @@
         <v>7.8</v>
       </c>
       <c r="J1078">
-        <v>0.39</v>
+        <v>31.32</v>
       </c>
     </row>
     <row r="1079">
@@ -36860,7 +36860,7 @@
         <v>10.75</v>
       </c>
       <c r="J1080">
-        <v>0.35</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1081">
@@ -36918,7 +36918,7 @@
         <v>10.05</v>
       </c>
       <c r="J1082">
-        <v>0.43</v>
+        <v>34.64</v>
       </c>
     </row>
     <row r="1083">
@@ -36976,7 +36976,7 @@
         <v>10.4</v>
       </c>
       <c r="J1084">
-        <v>0.39</v>
+        <v>31.09</v>
       </c>
     </row>
     <row r="1085">
@@ -37014,7 +37014,7 @@
         <v>12.08</v>
       </c>
       <c r="J1085">
-        <v>0.37</v>
+        <v>29.44</v>
       </c>
     </row>
     <row r="1086">
@@ -37052,7 +37052,7 @@
         <v>10.67</v>
       </c>
       <c r="J1086">
-        <v>0.45</v>
+        <v>36.04</v>
       </c>
     </row>
     <row r="1087">
@@ -37090,7 +37090,7 @@
         <v>11.34</v>
       </c>
       <c r="J1087">
-        <v>0.4</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="1088">
@@ -37128,7 +37128,7 @@
         <v>12.81</v>
       </c>
       <c r="J1088">
-        <v>0.4</v>
+        <v>31.82</v>
       </c>
     </row>
     <row r="1089">
@@ -37166,7 +37166,7 @@
         <v>12.17</v>
       </c>
       <c r="J1089">
-        <v>0.48</v>
+        <v>38.33</v>
       </c>
     </row>
     <row r="1090">
@@ -37204,7 +37204,7 @@
         <v>13.01</v>
       </c>
       <c r="J1090">
-        <v>0.43</v>
+        <v>34.61</v>
       </c>
     </row>
     <row r="1091">
@@ -37242,7 +37242,7 @@
         <v>12.6</v>
       </c>
       <c r="J1091">
-        <v>0.4</v>
+        <v>32.23</v>
       </c>
     </row>
     <row r="1092">
@@ -37280,7 +37280,7 @@
         <v>12.73</v>
       </c>
       <c r="J1092">
-        <v>0.48</v>
+        <v>38.72</v>
       </c>
     </row>
     <row r="1093">
@@ -37318,7 +37318,7 @@
         <v>12.88</v>
       </c>
       <c r="J1093">
-        <v>0.43</v>
+        <v>34.66</v>
       </c>
     </row>
     <row r="1094">
@@ -37893,7 +37893,7 @@
         <v>4.7</v>
       </c>
       <c r="J1112">
-        <v>0.46</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="1113">
@@ -37928,7 +37928,7 @@
         <v>5.1</v>
       </c>
       <c r="J1113">
-        <v>0.64</v>
+        <v>51.19</v>
       </c>
     </row>
     <row r="1114">
@@ -37963,7 +37963,7 @@
         <v>4.9</v>
       </c>
       <c r="J1114">
-        <v>0.52</v>
+        <v>41.83</v>
       </c>
     </row>
     <row r="1115">
@@ -37998,7 +37998,7 @@
         <v>5.25</v>
       </c>
       <c r="J1115">
-        <v>0.48</v>
+        <v>38.63</v>
       </c>
     </row>
     <row r="1116">
@@ -38033,7 +38033,7 @@
         <v>5.15</v>
       </c>
       <c r="J1116">
-        <v>0.67</v>
+        <v>53.87</v>
       </c>
     </row>
     <row r="1117">
@@ -38068,7 +38068,7 @@
         <v>5.2</v>
       </c>
       <c r="J1117">
-        <v>0.55</v>
+        <v>43.88</v>
       </c>
     </row>
     <row r="1118">
@@ -38103,7 +38103,7 @@
         <v>4.3</v>
       </c>
       <c r="J1118">
-        <v>0.47</v>
+        <v>37.37</v>
       </c>
     </row>
     <row r="1119">
@@ -38138,7 +38138,7 @@
         <v>3.5</v>
       </c>
       <c r="J1119">
-        <v>0.66</v>
+        <v>53.08</v>
       </c>
     </row>
     <row r="1120">
@@ -38173,7 +38173,7 @@
         <v>3.9</v>
       </c>
       <c r="J1120">
-        <v>0.54</v>
+        <v>43.49</v>
       </c>
     </row>
     <row r="1121">
@@ -38208,7 +38208,7 @@
         <v>5.6</v>
       </c>
       <c r="J1121">
-        <v>0.44</v>
+        <v>34.92</v>
       </c>
     </row>
     <row r="1122">
@@ -38243,7 +38243,7 @@
         <v>5.4</v>
       </c>
       <c r="J1122">
-        <v>0.61</v>
+        <v>48.89</v>
       </c>
     </row>
     <row r="1123">
@@ -38278,7 +38278,7 @@
         <v>5.5</v>
       </c>
       <c r="J1123">
-        <v>0.5</v>
+        <v>40.34</v>
       </c>
     </row>
     <row r="1124">
@@ -38316,7 +38316,7 @@
         <v>5.6</v>
       </c>
       <c r="J1124">
-        <v>0.41</v>
+        <v>32.67</v>
       </c>
     </row>
     <row r="1125">
@@ -38354,7 +38354,7 @@
         <v>5.8</v>
       </c>
       <c r="J1125">
-        <v>0.55</v>
+        <v>44.05</v>
       </c>
     </row>
     <row r="1126">
@@ -38392,7 +38392,7 @@
         <v>5.7</v>
       </c>
       <c r="J1126">
-        <v>0.46</v>
+        <v>36.75</v>
       </c>
     </row>
     <row r="1127">
@@ -38430,7 +38430,7 @@
         <v>6.2</v>
       </c>
       <c r="J1127">
-        <v>0.41</v>
+        <v>32.88</v>
       </c>
     </row>
     <row r="1128">
@@ -38468,7 +38468,7 @@
         <v>6</v>
       </c>
       <c r="J1128">
-        <v>0.57</v>
+        <v>45.74</v>
       </c>
     </row>
     <row r="1129">
@@ -38506,7 +38506,7 @@
         <v>6.1</v>
       </c>
       <c r="J1129">
-        <v>0.47</v>
+        <v>37.26</v>
       </c>
     </row>
     <row r="1130">
@@ -38544,7 +38544,7 @@
         <v>6.65</v>
       </c>
       <c r="J1130">
-        <v>0.42</v>
+        <v>33.64</v>
       </c>
     </row>
     <row r="1131">
@@ -38582,7 +38582,7 @@
         <v>6.35</v>
       </c>
       <c r="J1131">
-        <v>0.58</v>
+        <v>46.72</v>
       </c>
     </row>
     <row r="1132">
@@ -38620,7 +38620,7 @@
         <v>6.5</v>
       </c>
       <c r="J1132">
-        <v>0.48</v>
+        <v>38.34</v>
       </c>
     </row>
     <row r="1133">
@@ -38658,7 +38658,7 @@
         <v>6</v>
       </c>
       <c r="J1133">
-        <v>0.43</v>
+        <v>34.69</v>
       </c>
     </row>
     <row r="1134">
@@ -38696,7 +38696,7 @@
         <v>5.8</v>
       </c>
       <c r="J1134">
-        <v>0.59</v>
+        <v>47.41</v>
       </c>
     </row>
     <row r="1135">
@@ -38734,7 +38734,7 @@
         <v>5.9</v>
       </c>
       <c r="J1135">
-        <v>0.49</v>
+        <v>39.36</v>
       </c>
     </row>
     <row r="1136">
@@ -38772,7 +38772,7 @@
         <v>5.3</v>
       </c>
       <c r="J1136">
-        <v>0.46</v>
+        <v>36.81</v>
       </c>
     </row>
     <row r="1137">
@@ -38810,7 +38810,7 @@
         <v>5.5</v>
       </c>
       <c r="J1137">
-        <v>0.64</v>
+        <v>50.86</v>
       </c>
     </row>
     <row r="1138">
@@ -38848,7 +38848,7 @@
         <v>5.4</v>
       </c>
       <c r="J1138">
-        <v>0.52</v>
+        <v>41.87</v>
       </c>
     </row>
     <row r="1139">
@@ -38886,7 +38886,7 @@
         <v>8.449999999999999</v>
       </c>
       <c r="J1139">
-        <v>0.47</v>
+        <v>37.24</v>
       </c>
     </row>
     <row r="1140">
@@ -38924,7 +38924,7 @@
         <v>8.550000000000001</v>
       </c>
       <c r="J1140">
-        <v>0.61</v>
+        <v>48.56</v>
       </c>
     </row>
     <row r="1141">
@@ -38962,7 +38962,7 @@
         <v>8.5</v>
       </c>
       <c r="J1141">
-        <v>0.52</v>
+        <v>41.85</v>
       </c>
     </row>
     <row r="1142">
@@ -39000,7 +39000,7 @@
         <v>8.5</v>
       </c>
       <c r="J1142">
-        <v>0.48</v>
+        <v>38.45</v>
       </c>
     </row>
     <row r="1143">
@@ -39038,7 +39038,7 @@
         <v>7.9</v>
       </c>
       <c r="J1143">
-        <v>0.61</v>
+        <v>48.72</v>
       </c>
     </row>
     <row r="1144">
@@ -39076,7 +39076,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J1144">
-        <v>0.54</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="1145">
@@ -39134,7 +39134,7 @@
         <v>9.1</v>
       </c>
       <c r="J1146">
-        <v>0.47</v>
+        <v>37.81</v>
       </c>
     </row>
     <row r="1147">
@@ -39192,7 +39192,7 @@
         <v>8.5</v>
       </c>
       <c r="J1148">
-        <v>0.6</v>
+        <v>47.73</v>
       </c>
     </row>
     <row r="1149">
@@ -39250,7 +39250,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="J1150">
-        <v>0.52</v>
+        <v>41.62</v>
       </c>
     </row>
     <row r="1151">
@@ -39308,7 +39308,7 @@
         <v>7.45</v>
       </c>
       <c r="J1152">
-        <v>0.46</v>
+        <v>36.89</v>
       </c>
     </row>
     <row r="1153">
@@ -39366,7 +39366,7 @@
         <v>6.95</v>
       </c>
       <c r="J1154">
-        <v>0.59</v>
+        <v>47.21</v>
       </c>
     </row>
     <row r="1155">
@@ -39424,7 +39424,7 @@
         <v>7.2</v>
       </c>
       <c r="J1156">
-        <v>0.51</v>
+        <v>40.75</v>
       </c>
     </row>
     <row r="1157">
@@ -39482,7 +39482,7 @@
         <v>10.75</v>
       </c>
       <c r="J1158">
-        <v>0.48</v>
+        <v>38.51</v>
       </c>
     </row>
     <row r="1159">
@@ -39540,7 +39540,7 @@
         <v>10.05</v>
       </c>
       <c r="J1160">
-        <v>0.57</v>
+        <v>45.98</v>
       </c>
     </row>
     <row r="1161">
@@ -39598,7 +39598,7 @@
         <v>10.4</v>
       </c>
       <c r="J1162">
-        <v>0.51</v>
+        <v>40.92</v>
       </c>
     </row>
     <row r="1163">
@@ -39636,7 +39636,7 @@
         <v>10.13</v>
       </c>
       <c r="J1163">
-        <v>0.53</v>
+        <v>42.45</v>
       </c>
     </row>
     <row r="1164">
@@ -39674,7 +39674,7 @@
         <v>9.42</v>
       </c>
       <c r="J1164">
-        <v>0.62</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="1165">
@@ -39712,7 +39712,7 @@
         <v>9.57</v>
       </c>
       <c r="J1165">
-        <v>0.55</v>
+        <v>44.38</v>
       </c>
     </row>
     <row r="1166">
@@ -39750,7 +39750,7 @@
         <v>10.64</v>
       </c>
       <c r="J1166">
-        <v>0.5600000000000001</v>
+        <v>45.05</v>
       </c>
     </row>
     <row r="1167">
@@ -39788,7 +39788,7 @@
         <v>9.73</v>
       </c>
       <c r="J1167">
-        <v>0.64</v>
+        <v>51.16</v>
       </c>
     </row>
     <row r="1168">
@@ -39826,7 +39826,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="J1168">
-        <v>0.58</v>
+        <v>46.39</v>
       </c>
     </row>
     <row r="1169">
@@ -39864,7 +39864,7 @@
         <v>10.89</v>
       </c>
       <c r="J1169">
-        <v>0.58</v>
+        <v>46.51</v>
       </c>
     </row>
     <row r="1170">
@@ -39902,7 +39902,7 @@
         <v>9.44</v>
       </c>
       <c r="J1170">
-        <v>0.66</v>
+        <v>52.52</v>
       </c>
     </row>
     <row r="1171">
@@ -39940,7 +39940,7 @@
         <v>9.73</v>
       </c>
       <c r="J1171">
-        <v>0.6</v>
+        <v>47.69</v>
       </c>
     </row>
     <row r="1172">
@@ -40323,7 +40323,7 @@
         <v>3.8</v>
       </c>
       <c r="J1184">
-        <v>0.5600000000000001</v>
+        <v>44.66</v>
       </c>
     </row>
     <row r="1185">
@@ -40358,7 +40358,7 @@
         <v>3.2</v>
       </c>
       <c r="J1185">
-        <v>0.77</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="1186">
@@ -40393,7 +40393,7 @@
         <v>3.5</v>
       </c>
       <c r="J1186">
-        <v>0.63</v>
+        <v>50.57</v>
       </c>
     </row>
     <row r="1187">
@@ -40428,7 +40428,7 @@
         <v>5.5</v>
       </c>
       <c r="J1187">
-        <v>0.46</v>
+        <v>36.92</v>
       </c>
     </row>
     <row r="1188">
@@ -40463,7 +40463,7 @@
         <v>5.1</v>
       </c>
       <c r="J1188">
-        <v>0.62</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="1189">
@@ -40498,7 +40498,7 @@
         <v>5.3</v>
       </c>
       <c r="J1189">
-        <v>0.51</v>
+        <v>41.15</v>
       </c>
     </row>
     <row r="1190">
@@ -40533,7 +40533,7 @@
         <v>3.1</v>
       </c>
       <c r="J1190">
-        <v>0.42</v>
+        <v>33.42</v>
       </c>
     </row>
     <row r="1191">
@@ -40568,7 +40568,7 @@
         <v>3.5</v>
       </c>
       <c r="J1191">
-        <v>0.59</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="1192">
@@ -40603,7 +40603,7 @@
         <v>3.3</v>
       </c>
       <c r="J1192">
-        <v>0.48</v>
+        <v>38.29</v>
       </c>
     </row>
     <row r="1193">
@@ -40638,7 +40638,7 @@
         <v>2.65</v>
       </c>
       <c r="J1193">
-        <v>0.39</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="1194">
@@ -40673,7 +40673,7 @@
         <v>2.55</v>
       </c>
       <c r="J1194">
-        <v>0.5600000000000001</v>
+        <v>44.47</v>
       </c>
     </row>
     <row r="1195">
@@ -40708,7 +40708,7 @@
         <v>2.6</v>
       </c>
       <c r="J1195">
-        <v>0.45</v>
+        <v>35.71</v>
       </c>
     </row>
     <row r="1196">
@@ -40743,7 +40743,7 @@
         <v>5.5</v>
       </c>
       <c r="J1196">
-        <v>0.37</v>
+        <v>29.55</v>
       </c>
     </row>
     <row r="1197">
@@ -40778,7 +40778,7 @@
         <v>4.7</v>
       </c>
       <c r="J1197">
-        <v>0.52</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="1198">
@@ -40813,7 +40813,7 @@
         <v>5.1</v>
       </c>
       <c r="J1198">
-        <v>0.43</v>
+        <v>34.19</v>
       </c>
     </row>
     <row r="1199">
@@ -40848,7 +40848,7 @@
         <v>7.6</v>
       </c>
       <c r="J1199">
-        <v>0.34</v>
+        <v>26.85</v>
       </c>
     </row>
     <row r="1200">
@@ -40883,7 +40883,7 @@
         <v>7.4</v>
       </c>
       <c r="J1200">
-        <v>0.49</v>
+        <v>38.94</v>
       </c>
     </row>
     <row r="1201">
@@ -40918,7 +40918,7 @@
         <v>7.5</v>
       </c>
       <c r="J1201">
-        <v>0.39</v>
+        <v>31.53</v>
       </c>
     </row>
     <row r="1202">
@@ -40956,7 +40956,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="J1202">
-        <v>0.32</v>
+        <v>25.76</v>
       </c>
     </row>
     <row r="1203">
@@ -40994,7 +40994,7 @@
         <v>8.5</v>
       </c>
       <c r="J1203">
-        <v>0.45</v>
+        <v>36.22</v>
       </c>
     </row>
     <row r="1204">
@@ -41032,7 +41032,7 @@
         <v>8.4</v>
       </c>
       <c r="J1204">
-        <v>0.38</v>
+        <v>30.08</v>
       </c>
     </row>
     <row r="1205">
@@ -41070,7 +41070,7 @@
         <v>6.6</v>
       </c>
       <c r="J1205">
-        <v>0.31</v>
+        <v>24.82</v>
       </c>
     </row>
     <row r="1206">
@@ -41108,7 +41108,7 @@
         <v>6.4</v>
       </c>
       <c r="J1206">
-        <v>0.46</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1207">
@@ -41146,7 +41146,7 @@
         <v>6.5</v>
       </c>
       <c r="J1207">
-        <v>0.36</v>
+        <v>28.91</v>
       </c>
     </row>
     <row r="1208">
@@ -41184,7 +41184,7 @@
         <v>5.45</v>
       </c>
       <c r="J1208">
-        <v>0.32</v>
+        <v>25.39</v>
       </c>
     </row>
     <row r="1209">
@@ -41222,7 +41222,7 @@
         <v>5.15</v>
       </c>
       <c r="J1209">
-        <v>0.47</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="1210">
@@ -41260,7 +41260,7 @@
         <v>5.3</v>
       </c>
       <c r="J1210">
-        <v>0.37</v>
+        <v>29.64</v>
       </c>
     </row>
     <row r="1211">
@@ -41298,7 +41298,7 @@
         <v>5.9</v>
       </c>
       <c r="J1211">
-        <v>0.32</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1212">
@@ -41336,7 +41336,7 @@
         <v>5.7</v>
       </c>
       <c r="J1212">
-        <v>0.49</v>
+        <v>39.32</v>
       </c>
     </row>
     <row r="1213">
@@ -41374,7 +41374,7 @@
         <v>5.8</v>
       </c>
       <c r="J1213">
-        <v>0.38</v>
+        <v>30.79</v>
       </c>
     </row>
     <row r="1214">
@@ -41412,7 +41412,7 @@
         <v>4.4</v>
       </c>
       <c r="J1214">
-        <v>0.33</v>
+        <v>26.68</v>
       </c>
     </row>
     <row r="1215">
@@ -41450,7 +41450,7 @@
         <v>4.6</v>
       </c>
       <c r="J1215">
-        <v>0.48</v>
+        <v>38.78</v>
       </c>
     </row>
     <row r="1216">
@@ -41488,7 +41488,7 @@
         <v>4.5</v>
       </c>
       <c r="J1216">
-        <v>0.39</v>
+        <v>31.07</v>
       </c>
     </row>
     <row r="1217">
@@ -41526,7 +41526,7 @@
         <v>4.75</v>
       </c>
       <c r="J1217">
-        <v>0.35</v>
+        <v>27.66</v>
       </c>
     </row>
     <row r="1218">
@@ -41564,7 +41564,7 @@
         <v>4.85</v>
       </c>
       <c r="J1218">
-        <v>0.49</v>
+        <v>39.34</v>
       </c>
     </row>
     <row r="1219">
@@ -41602,7 +41602,7 @@
         <v>4.8</v>
       </c>
       <c r="J1219">
-        <v>0.39</v>
+        <v>31.53</v>
       </c>
     </row>
     <row r="1220">
@@ -41640,7 +41640,7 @@
         <v>12</v>
       </c>
       <c r="J1220">
-        <v>0.35</v>
+        <v>28.32</v>
       </c>
     </row>
     <row r="1221">
@@ -41678,7 +41678,7 @@
         <v>11.4</v>
       </c>
       <c r="J1221">
-        <v>0.5</v>
+        <v>40.19</v>
       </c>
     </row>
     <row r="1222">
@@ -41716,7 +41716,7 @@
         <v>11.7</v>
       </c>
       <c r="J1222">
-        <v>0.41</v>
+        <v>32.76</v>
       </c>
     </row>
     <row r="1223">
@@ -41774,7 +41774,7 @@
         <v>10.3</v>
       </c>
       <c r="J1224">
-        <v>0.36</v>
+        <v>28.94</v>
       </c>
     </row>
     <row r="1225">
@@ -41832,7 +41832,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="J1226">
-        <v>0.5</v>
+        <v>40.22</v>
       </c>
     </row>
     <row r="1227">
@@ -41890,7 +41890,7 @@
         <v>10</v>
       </c>
       <c r="J1228">
-        <v>0.41</v>
+        <v>32.72</v>
       </c>
     </row>
     <row r="1229">
@@ -41948,7 +41948,7 @@
         <v>7.85</v>
       </c>
       <c r="J1230">
-        <v>0.36</v>
+        <v>28.63</v>
       </c>
     </row>
     <row r="1231">
@@ -42006,7 +42006,7 @@
         <v>7.35</v>
       </c>
       <c r="J1232">
-        <v>0.49</v>
+        <v>38.91</v>
       </c>
     </row>
     <row r="1233">
@@ -42064,7 +42064,7 @@
         <v>7.6</v>
       </c>
       <c r="J1234">
-        <v>0.4</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="1235">
@@ -42122,7 +42122,7 @@
         <v>9.35</v>
       </c>
       <c r="J1236">
-        <v>0.37</v>
+        <v>29.71</v>
       </c>
     </row>
     <row r="1237">
@@ -42180,7 +42180,7 @@
         <v>8.65</v>
       </c>
       <c r="J1238">
-        <v>0.48</v>
+        <v>38.47</v>
       </c>
     </row>
     <row r="1239">
@@ -42238,7 +42238,7 @@
         <v>9</v>
       </c>
       <c r="J1240">
-        <v>0.41</v>
+        <v>32.55</v>
       </c>
     </row>
     <row r="1241">
@@ -42276,7 +42276,7 @@
         <v>8.539999999999999</v>
       </c>
       <c r="J1241">
-        <v>0.39</v>
+        <v>31.29</v>
       </c>
     </row>
     <row r="1242">
@@ -42314,7 +42314,7 @@
         <v>8.43</v>
       </c>
       <c r="J1242">
-        <v>0.52</v>
+        <v>41.21</v>
       </c>
     </row>
     <row r="1243">
@@ -42352,7 +42352,7 @@
         <v>8.35</v>
       </c>
       <c r="J1243">
-        <v>0.44</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="1244">
@@ -42390,7 +42390,7 @@
         <v>9.24</v>
       </c>
       <c r="J1244">
-        <v>0.43</v>
+        <v>34.04</v>
       </c>
     </row>
     <row r="1245">
@@ -42428,7 +42428,7 @@
         <v>9.18</v>
       </c>
       <c r="J1245">
-        <v>0.54</v>
+        <v>43.22</v>
       </c>
     </row>
     <row r="1246">
@@ -42466,7 +42466,7 @@
         <v>9.359999999999999</v>
       </c>
       <c r="J1246">
-        <v>0.47</v>
+        <v>37.29</v>
       </c>
     </row>
     <row r="1247">
@@ -42504,7 +42504,7 @@
         <v>9.15</v>
       </c>
       <c r="J1247">
-        <v>0.45</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="1248">
@@ -42542,7 +42542,7 @@
         <v>8.77</v>
       </c>
       <c r="J1248">
-        <v>0.5600000000000001</v>
+        <v>44.75</v>
       </c>
     </row>
     <row r="1249">
@@ -42580,7 +42580,7 @@
         <v>8.93</v>
       </c>
       <c r="J1249">
-        <v>0.48</v>
+        <v>38.59</v>
       </c>
     </row>
     <row r="1250">
@@ -42963,7 +42963,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="J1262">
-        <v>0.46</v>
+        <v>36.65</v>
       </c>
     </row>
     <row r="1263">
@@ -42998,7 +42998,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J1263">
-        <v>0.59</v>
+        <v>47.34</v>
       </c>
     </row>
     <row r="1264">
@@ -43033,7 +43033,7 @@
         <v>8.5</v>
       </c>
       <c r="J1264">
-        <v>0.49</v>
+        <v>39.52</v>
       </c>
     </row>
     <row r="1265">
@@ -43068,7 +43068,7 @@
         <v>18.3</v>
       </c>
       <c r="J1265">
-        <v>0.39</v>
+        <v>31.21</v>
       </c>
     </row>
     <row r="1266">
@@ -43103,7 +43103,7 @@
         <v>17.9</v>
       </c>
       <c r="J1266">
-        <v>0.51</v>
+        <v>41.01</v>
       </c>
     </row>
     <row r="1267">
@@ -43138,7 +43138,7 @@
         <v>18.1</v>
       </c>
       <c r="J1267">
-        <v>0.42</v>
+        <v>33.63</v>
       </c>
     </row>
     <row r="1268">
@@ -43173,7 +43173,7 @@
         <v>20.2</v>
       </c>
       <c r="J1268">
-        <v>0.35</v>
+        <v>28.29</v>
       </c>
     </row>
     <row r="1269">
@@ -43208,7 +43208,7 @@
         <v>20.6</v>
       </c>
       <c r="J1269">
-        <v>0.47</v>
+        <v>37.58</v>
       </c>
     </row>
     <row r="1270">
@@ -43243,7 +43243,7 @@
         <v>20.4</v>
       </c>
       <c r="J1270">
-        <v>0.39</v>
+        <v>31.38</v>
       </c>
     </row>
     <row r="1271">
@@ -43278,7 +43278,7 @@
         <v>11.15</v>
       </c>
       <c r="J1271">
-        <v>0.35</v>
+        <v>27.92</v>
       </c>
     </row>
     <row r="1272">
@@ -43313,7 +43313,7 @@
         <v>11.05</v>
       </c>
       <c r="J1272">
-        <v>0.44</v>
+        <v>34.96</v>
       </c>
     </row>
     <row r="1273">
@@ -43348,7 +43348,7 @@
         <v>11.1</v>
       </c>
       <c r="J1273">
-        <v>0.38</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1274">
@@ -43383,7 +43383,7 @@
         <v>14.5</v>
       </c>
       <c r="J1274">
-        <v>0.35</v>
+        <v>27.67</v>
       </c>
     </row>
     <row r="1275">
@@ -43418,7 +43418,7 @@
         <v>13.7</v>
       </c>
       <c r="J1275">
-        <v>0.45</v>
+        <v>36.04</v>
       </c>
     </row>
     <row r="1276">
@@ -43453,7 +43453,7 @@
         <v>14.1</v>
       </c>
       <c r="J1276">
-        <v>0.38</v>
+        <v>30.19</v>
       </c>
     </row>
     <row r="1277">
@@ -43488,7 +43488,7 @@
         <v>24.6</v>
       </c>
       <c r="J1277">
-        <v>0.32</v>
+        <v>25.54</v>
       </c>
     </row>
     <row r="1278">
@@ -43523,7 +43523,7 @@
         <v>24.4</v>
       </c>
       <c r="J1278">
-        <v>0.44</v>
+        <v>35.31</v>
       </c>
     </row>
     <row r="1279">
@@ -43558,7 +43558,7 @@
         <v>24.5</v>
       </c>
       <c r="J1279">
-        <v>0.36</v>
+        <v>28.52</v>
       </c>
     </row>
     <row r="1280">
@@ -43596,7 +43596,7 @@
         <v>19.4</v>
       </c>
       <c r="J1280">
-        <v>0.31</v>
+        <v>24.63</v>
       </c>
     </row>
     <row r="1281">
@@ -43634,7 +43634,7 @@
         <v>19.6</v>
       </c>
       <c r="J1281">
-        <v>0.42</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="1282">
@@ -43672,7 +43672,7 @@
         <v>19.5</v>
       </c>
       <c r="J1282">
-        <v>0.34</v>
+        <v>27.38</v>
       </c>
     </row>
     <row r="1283">
@@ -43710,7 +43710,7 @@
         <v>17.2</v>
       </c>
       <c r="J1283">
-        <v>0.3</v>
+        <v>24.09</v>
       </c>
     </row>
     <row r="1284">
@@ -43748,7 +43748,7 @@
         <v>17</v>
       </c>
       <c r="J1284">
-        <v>0.41</v>
+        <v>32.84</v>
       </c>
     </row>
     <row r="1285">
@@ -43786,7 +43786,7 @@
         <v>17.1</v>
       </c>
       <c r="J1285">
-        <v>0.33</v>
+        <v>26.57</v>
       </c>
     </row>
     <row r="1286">
@@ -43824,7 +43824,7 @@
         <v>15.05</v>
       </c>
       <c r="J1286">
-        <v>0.31</v>
+        <v>24.92</v>
       </c>
     </row>
     <row r="1287">
@@ -43862,7 +43862,7 @@
         <v>14.75</v>
       </c>
       <c r="J1287">
-        <v>0.42</v>
+        <v>33.78</v>
       </c>
     </row>
     <row r="1288">
@@ -43900,7 +43900,7 @@
         <v>14.9</v>
       </c>
       <c r="J1288">
-        <v>0.35</v>
+        <v>27.79</v>
       </c>
     </row>
     <row r="1289">
@@ -43938,7 +43938,7 @@
         <v>17</v>
       </c>
       <c r="J1289">
-        <v>0.32</v>
+        <v>25.47</v>
       </c>
     </row>
     <row r="1290">
@@ -43976,7 +43976,7 @@
         <v>16.8</v>
       </c>
       <c r="J1290">
-        <v>0.43</v>
+        <v>34.44</v>
       </c>
     </row>
     <row r="1291">
@@ -44014,7 +44014,7 @@
         <v>16.9</v>
       </c>
       <c r="J1291">
-        <v>0.35</v>
+        <v>28.31</v>
       </c>
     </row>
     <row r="1292">
@@ -44052,7 +44052,7 @@
         <v>14.8</v>
       </c>
       <c r="J1292">
-        <v>0.34</v>
+        <v>27.58</v>
       </c>
     </row>
     <row r="1293">
@@ -44090,7 +44090,7 @@
         <v>15</v>
       </c>
       <c r="J1293">
-        <v>0.45</v>
+        <v>35.68</v>
       </c>
     </row>
     <row r="1294">
@@ -44128,7 +44128,7 @@
         <v>14.9</v>
       </c>
       <c r="J1294">
-        <v>0.37</v>
+        <v>29.66</v>
       </c>
     </row>
     <row r="1295">
@@ -44166,7 +44166,7 @@
         <v>11.55</v>
       </c>
       <c r="J1295">
-        <v>0.36</v>
+        <v>28.97</v>
       </c>
     </row>
     <row r="1296">
@@ -44204,7 +44204,7 @@
         <v>11.65</v>
       </c>
       <c r="J1296">
-        <v>0.47</v>
+        <v>37.48</v>
       </c>
     </row>
     <row r="1297">
@@ -44242,7 +44242,7 @@
         <v>11.6</v>
       </c>
       <c r="J1297">
-        <v>0.39</v>
+        <v>31.57</v>
       </c>
     </row>
     <row r="1298">
@@ -44280,7 +44280,7 @@
         <v>15.8</v>
       </c>
       <c r="J1298">
-        <v>0.36</v>
+        <v>29.01</v>
       </c>
     </row>
     <row r="1299">
@@ -44318,7 +44318,7 @@
         <v>15.2</v>
       </c>
       <c r="J1299">
-        <v>0.48</v>
+        <v>38.12</v>
       </c>
     </row>
     <row r="1300">
@@ -44356,7 +44356,7 @@
         <v>15.5</v>
       </c>
       <c r="J1300">
-        <v>0.4</v>
+        <v>31.66</v>
       </c>
     </row>
     <row r="1301">
@@ -44414,7 +44414,7 @@
         <v>21.6</v>
       </c>
       <c r="J1302">
-        <v>0.38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1303">
@@ -44472,7 +44472,7 @@
         <v>21</v>
       </c>
       <c r="J1304">
-        <v>0.49</v>
+        <v>39.21</v>
       </c>
     </row>
     <row r="1305">
@@ -44530,7 +44530,7 @@
         <v>21.3</v>
       </c>
       <c r="J1306">
-        <v>0.41</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="1307">
@@ -44588,7 +44588,7 @@
         <v>12.55</v>
       </c>
       <c r="J1308">
-        <v>0.39</v>
+        <v>31.44</v>
       </c>
     </row>
     <row r="1309">
@@ -44646,7 +44646,7 @@
         <v>12.05</v>
       </c>
       <c r="J1310">
-        <v>0.5</v>
+        <v>39.91</v>
       </c>
     </row>
     <row r="1311">
@@ -44704,7 +44704,7 @@
         <v>12.3</v>
       </c>
       <c r="J1312">
-        <v>0.43</v>
+        <v>34.05</v>
       </c>
     </row>
     <row r="1313">
@@ -44762,7 +44762,7 @@
         <v>16.95</v>
       </c>
       <c r="J1314">
-        <v>0.4</v>
+        <v>31.92</v>
       </c>
     </row>
     <row r="1315">
@@ -44820,7 +44820,7 @@
         <v>16.25</v>
       </c>
       <c r="J1316">
-        <v>0.51</v>
+        <v>40.92</v>
       </c>
     </row>
     <row r="1317">
@@ -44878,7 +44878,7 @@
         <v>16.6</v>
       </c>
       <c r="J1318">
-        <v>0.43</v>
+        <v>34.12</v>
       </c>
     </row>
     <row r="1319">
@@ -44916,7 +44916,7 @@
         <v>16.88</v>
       </c>
       <c r="J1319">
-        <v>0.42</v>
+        <v>33.44</v>
       </c>
     </row>
     <row r="1320">
@@ -44954,7 +44954,7 @@
         <v>18.97</v>
       </c>
       <c r="J1320">
-        <v>0.53</v>
+        <v>42.69</v>
       </c>
     </row>
     <row r="1321">
@@ -44992,7 +44992,7 @@
         <v>17.25</v>
       </c>
       <c r="J1321">
-        <v>0.45</v>
+        <v>35.79</v>
       </c>
     </row>
     <row r="1322">
@@ -45030,7 +45030,7 @@
         <v>15.38</v>
       </c>
       <c r="J1322">
-        <v>0.44</v>
+        <v>34.98</v>
       </c>
     </row>
     <row r="1323">
@@ -45068,7 +45068,7 @@
         <v>14.86</v>
       </c>
       <c r="J1323">
-        <v>0.55</v>
+        <v>44.07</v>
       </c>
     </row>
     <row r="1324">
@@ -45106,7 +45106,7 @@
         <v>14.78</v>
       </c>
       <c r="J1324">
-        <v>0.47</v>
+        <v>37.26</v>
       </c>
     </row>
     <row r="1325">
@@ -45144,7 +45144,7 @@
         <v>15.33</v>
       </c>
       <c r="J1325">
-        <v>0.44</v>
+        <v>35.46</v>
       </c>
     </row>
     <row r="1326">
@@ -45182,7 +45182,7 @@
         <v>15.63</v>
       </c>
       <c r="J1326">
-        <v>0.55</v>
+        <v>44.18</v>
       </c>
     </row>
     <row r="1327">
@@ -45220,7 +45220,7 @@
         <v>15.39</v>
       </c>
       <c r="J1327">
-        <v>0.47</v>
+        <v>37.28</v>
       </c>
     </row>
   </sheetData>
